--- a/testResults/compilerResults/CompilerResults.xlsx
+++ b/testResults/compilerResults/CompilerResults.xlsx
@@ -16,12 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
-    <t>Settings</t>
+    <t>Resolution</t>
   </si>
   <si>
-    <t xml:space="preserve">Time (hr)</t>
+    <t>T</t>
+  </si>
+  <si>
+    <t>dt</t>
+  </si>
+  <si>
+    <t>Cores</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
   <si>
     <t xml:space="preserve">Time Sec</t>
@@ -30,52 +42,70 @@
     <t>Speedup</t>
   </si>
   <si>
-    <t>core</t>
+    <t xml:space="preserve">No Data Saved</t>
   </si>
   <si>
-    <t>resol</t>
+    <t>def-bprotas</t>
   </si>
   <si>
-    <t>alpha</t>
+    <t xml:space="preserve">full node</t>
   </si>
   <si>
-    <t>T</t>
+    <t xml:space="preserve">Time Hour</t>
   </si>
   <si>
-    <t>dt</t>
+    <t>Node</t>
   </si>
   <si>
-    <t xml:space="preserve">"-fopenmp -O3 -pg"</t>
+    <t>cores</t>
   </si>
   <si>
-    <t>32/256</t>
+    <t>id</t>
   </si>
   <si>
-    <t>2^-5</t>
+    <t xml:space="preserve">c494: 192</t>
   </si>
   <si>
-    <t xml:space="preserve">"-fopenmp -O3"</t>
+    <t xml:space="preserve">c299: 192</t>
   </si>
   <si>
-    <t xml:space="preserve">"-fopenmp -Ofast"</t>
+    <t xml:space="preserve">c465: 192</t>
   </si>
   <si>
-    <t xml:space="preserve">"-fopenmp -O3 -march=native"</t>
+    <t xml:space="preserve">c431: 192</t>
   </si>
   <si>
-    <t>"-O3"</t>
+    <t xml:space="preserve">c420: 192</t>
   </si>
   <si>
-    <t xml:space="preserve">"-O3 -funroll-loops"</t>
+    <t xml:space="preserve">c308: 192</t>
   </si>
   <si>
-    <t>"-Ofast"</t>
+    <t xml:space="preserve">c344: 192</t>
   </si>
   <si>
-    <t xml:space="preserve">"-O3 -march=native"</t>
+    <t xml:space="preserve">c343: 192</t>
   </si>
   <si>
-    <t xml:space="preserve">"-O3 -pg"</t>
+    <t xml:space="preserve">c663: 192</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">c692: 192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c651: 192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c540: 192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c360: 192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c435: 192</t>
   </si>
 </sst>
 </file>
@@ -85,12 +115,30 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,14 +161,34 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -136,6 +204,3785 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$D$2:$D$9</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$9</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
+        <c:axId val="2140841479"/>
+        <c:axId val="2140841480"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841480"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="6562723" y="757235"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$D$13:$D$20</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$13:$H$20</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
+        <c:axId val="2140841491"/>
+        <c:axId val="2140841492"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841491"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841492"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841492"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841491"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="6562722" y="3576635"/>
+      <a:ext cx="4552948" cy="2905124"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$D$44:$D$51</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$44:$H$51</c:f>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="2140841497"/>
+        <c:axId val="2140841498"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841497"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841498"/>
+        <c:crosses val="autoZero"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841498"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841497"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="7962899" y="7215187"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet1!$D$54:$D$61</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$54:$H$61</c:f>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="2140841503"/>
+        <c:axId val="2140841504"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2140841503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841504"/>
+        <c:crosses val="autoZero"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2140841504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841503"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="8229599" y="10120312"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466723</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>33336</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>142872</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>42860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="583946" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6562723" y="757235"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466722</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>138110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>142871</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>147636</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="493733528" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6562722" y="3576635"/>
+        <a:ext cx="4552948" cy="2905124"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="650898266" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="7962899" y="7215187"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="336452411" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="8229599" y="10120312"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,457 +4467,1883 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.28125"/>
-    <col bestFit="1" min="2" max="2" style="1" width="11.28125"/>
+    <col customWidth="1" min="1" max="1" width="11.140625"/>
+    <col customWidth="1" min="6" max="7" style="1" width="12.7109375"/>
+    <col customWidth="1" min="9" max="9" width="12.00390625"/>
+    <col bestFit="1" min="11" max="11" style="0" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="C2" s="2">
-        <f t="shared" ref="C2:C9" si="0">B2*3600</f>
-        <v>1620</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D7" si="1">C$2/C2</f>
+      <c r="A2" s="2">
+        <v>256</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>128</v>
-      </c>
-      <c r="F2">
-        <v>512</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
+        <f t="shared" ref="E2:E33" si="0">16/256</f>
+        <v>0.0625</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.015775462962962963</v>
+      </c>
+      <c r="G2" s="3">
+        <f t="shared" ref="G2:G9" si="1">HOUR(F2)*3600+MINUTE(F2)*60+SECOND(F2)</f>
+        <v>1363</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
+        <f t="shared" ref="H2:H9" si="2">G$2/G2</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1">
-        <f>(0.2913515875+0.246882429722222)/2</f>
-        <v>0.26911700861111099</v>
+      <c r="A3" s="2">
+        <v>256</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5</v>
       </c>
       <c r="C3" s="2">
+        <f t="shared" ref="C3:C33" si="3">2^(-5)</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
         <f t="shared" si="0"/>
-        <v>968.82123099999956</v>
-      </c>
-      <c r="D3">
+        <v>0.0625</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.0094907407407407406</v>
+      </c>
+      <c r="G3" s="3">
         <f t="shared" si="1"/>
-        <v>1.6721351144708767</v>
-      </c>
-      <c r="E3">
-        <v>128</v>
-      </c>
-      <c r="F3">
-        <v>512</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
+        <v>820</v>
       </c>
       <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>1.6621951219512194</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1.4199999999999999</v>
+      <c r="A4" s="4">
+        <v>256</v>
+      </c>
+      <c r="B4" s="4">
+        <v>5</v>
       </c>
       <c r="C4" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>5112</v>
-      </c>
-      <c r="D4">
+        <v>0.0625</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="G4" s="3">
         <f t="shared" si="1"/>
-        <v>0.31690140845070425</v>
-      </c>
-      <c r="E4">
-        <v>128</v>
-      </c>
-      <c r="F4">
-        <v>512</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>10</v>
+        <v>432</v>
       </c>
       <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>3.1550925925925926</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.27265931444444402</v>
+      <c r="A5" s="2">
+        <v>256</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5</v>
       </c>
       <c r="C5" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D5" s="2">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>981.57353199999852</v>
-      </c>
-      <c r="D5">
+        <v>0.0625</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.0030439814814814813</v>
+      </c>
+      <c r="G5" s="3">
         <f t="shared" si="1"/>
-        <v>1.6504112500865624</v>
-      </c>
-      <c r="E5">
-        <v>128</v>
-      </c>
-      <c r="F5">
-        <v>512</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>263</v>
       </c>
       <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>5.1825095057034218</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.26382738972222203</v>
+      <c r="A6" s="4">
+        <v>256</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5</v>
       </c>
       <c r="C6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D6" s="2">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>949.77860299999929</v>
-      </c>
-      <c r="D6">
+        <v>0.0625</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.0022106481481481482</v>
+      </c>
+      <c r="G6" s="3">
         <f t="shared" si="1"/>
-        <v>1.7056606612141179</v>
-      </c>
-      <c r="E6">
-        <v>128</v>
-      </c>
-      <c r="F6">
-        <v>512</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>10</v>
+        <v>191</v>
       </c>
       <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>7.1361256544502618</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.290683926944444</v>
+      <c r="A7" s="2">
+        <v>256</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
       </c>
       <c r="C7" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D7" s="2">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>1046.4621369999984</v>
-      </c>
-      <c r="D7">
+        <v>0.0625</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.0013888888888888889</v>
+      </c>
+      <c r="G7" s="3">
         <f t="shared" si="1"/>
-        <v>1.5480732104118187</v>
-      </c>
-      <c r="E7">
-        <v>128</v>
-      </c>
-      <c r="F7">
-        <v>512</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>11.358333333333333</v>
       </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="4">
+        <v>256</v>
+      </c>
+      <c r="B8" s="4">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D8" s="2">
+        <v>64</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.00099537037037037042</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>15.848837209302326</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <f>(1.23042868916667+1.3707738525)/2</f>
-        <v>1.300601270833335</v>
+      <c r="A9" s="2">
+        <v>256</v>
+      </c>
+      <c r="B9" s="2">
+        <v>5</v>
       </c>
       <c r="C9" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D9" s="2">
+        <v>128</v>
+      </c>
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>4682.1645750000062</v>
-      </c>
-      <c r="D9" s="3">
-        <f>C$9/C9</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>128</v>
-      </c>
-      <c r="F9" s="3">
-        <v>512</v>
-      </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3">
-        <v>25</v>
-      </c>
-      <c r="I9" t="s">
-        <v>11</v>
+        <v>0.0625</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.00089120370370370373</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>17.7012987012987</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1">
-        <f>(1.42444136055556+1.41068360194444)/2</f>
-        <v>1.4175624812500001</v>
+      <c r="A10" s="2">
+        <v>256</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" ref="C10:C14" si="2">B10*3600</f>
-        <v>5103.2249325000003</v>
-      </c>
-      <c r="D10" s="3">
-        <f t="shared" ref="D10:D14" si="3">C$9/C10</f>
-        <v>0.91749131910324744</v>
-      </c>
-      <c r="E10" s="3">
-        <v>128</v>
-      </c>
-      <c r="F10" s="3">
-        <v>512</v>
-      </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3">
-        <v>25</v>
-      </c>
-      <c r="I10" t="s">
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D10" s="2">
+        <v>256</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="3" t="e">
+        <f t="shared" ref="G10:G33" si="4">HOUR(F10)*3600+MINUTE(F10)*60+SECOND(F10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" t="e">
+        <f t="shared" ref="H10:H11" si="5">G$2/G10</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2.5</v>
+      <c r="A11">
+        <v>256</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="2"/>
-        <v>9000</v>
-      </c>
-      <c r="D11" s="3">
         <f t="shared" si="3"/>
-        <v>0.52024050833333402</v>
-      </c>
-      <c r="E11" s="3">
-        <v>128</v>
-      </c>
-      <c r="F11" s="3">
+        <v>0.03125</v>
+      </c>
+      <c r="D11">
         <v>512</v>
       </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="3">
-        <v>25</v>
-      </c>
-      <c r="I11" t="s">
-        <v>11</v>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G11" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H11" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2.1000000000000001</v>
-      </c>
-      <c r="C12" s="2">
-        <f t="shared" si="2"/>
-        <v>7560</v>
-      </c>
-      <c r="D12" s="3">
-        <f t="shared" si="3"/>
-        <v>0.61933393849206431</v>
-      </c>
-      <c r="E12" s="3">
-        <v>128</v>
-      </c>
-      <c r="F12" s="3">
-        <v>512</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3">
-        <v>25</v>
-      </c>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.35038762777778</v>
-      </c>
-      <c r="C13" s="2">
-        <f t="shared" si="2"/>
-        <v>4861.3954600000079</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="A13" s="2">
+        <v>512</v>
+      </c>
+      <c r="B13" s="2">
+        <v>5</v>
+      </c>
+      <c r="C13">
         <f t="shared" si="3"/>
-        <v>0.96313180310576885</v>
-      </c>
-      <c r="E13" s="3">
-        <v>128</v>
-      </c>
-      <c r="F13" s="3">
-        <v>512</v>
-      </c>
-      <c r="G13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="3">
-        <v>25</v>
-      </c>
-      <c r="I13" t="s">
-        <v>11</v>
+        <v>0.03125</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.13925925925925925</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="4"/>
+        <v>12032</v>
+      </c>
+      <c r="H13">
+        <f t="shared" ref="H13:H22" si="6">G$13/G13</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1.42375673222222</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="2"/>
-        <v>5125.524235999992</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="A14">
+        <v>512</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
         <f t="shared" si="3"/>
-        <v>0.91349964597065525</v>
-      </c>
-      <c r="E14" s="3">
-        <v>128</v>
-      </c>
-      <c r="F14" s="3">
-        <v>512</v>
-      </c>
-      <c r="G14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3">
-        <v>25</v>
-      </c>
-      <c r="I14" t="s">
-        <v>11</v>
+        <v>0.03125</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.090462962962962967</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="4"/>
+        <v>7816</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="6"/>
+        <v>1.5394063459570113</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" t="s">
+      <c r="A15">
+        <v>512</v>
+      </c>
+      <c r="B15" s="4">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.051249999999999997</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="4"/>
+        <v>4428</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="6"/>
+        <v>2.7172538392050587</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16">
+        <v>512</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.03366898148148148</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="4"/>
+        <v>2909</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="6"/>
+        <v>4.1361292540391883</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17">
+        <v>512</v>
+      </c>
+      <c r="B17" s="4">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.019965277777777776</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="4"/>
+        <v>1725</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="6"/>
+        <v>6.9750724637681163</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18">
+        <v>512</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D18">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.010659722222222221</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="4"/>
+        <v>921</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="6"/>
+        <v>13.064060803474485</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19">
+        <v>512</v>
+      </c>
+      <c r="B19" s="4">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D19">
+        <v>64</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.0086689814814814806</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="4"/>
+        <v>749</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="6"/>
+        <v>16.064085447263018</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20">
+        <v>512</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D20">
+        <v>128</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.0064583333333333333</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="4"/>
+        <v>558</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="6"/>
+        <v>21.562724014336919</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21">
+        <v>512</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D21">
+        <v>256</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G21" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H21" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22">
+        <v>512</v>
+      </c>
+      <c r="B22" s="4">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D22" s="4">
+        <v>512</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G22" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H22" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="2"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24">
+        <v>1024</v>
+      </c>
+      <c r="B24" s="4">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G24" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H24" t="e">
+        <f t="shared" ref="H24:H33" si="7">G$24/G24</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G25" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H25" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26">
+        <v>1024</v>
+      </c>
+      <c r="B26" s="4">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G26" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H26" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27">
+        <v>1024</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G27" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H27" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28">
+        <v>1024</v>
+      </c>
+      <c r="B28" s="4">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G28" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H28" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29">
+        <v>1024</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D29">
+        <v>32</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G29" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H29" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30">
+        <v>1024</v>
+      </c>
+      <c r="B30" s="4">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D30">
+        <v>64</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H30" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31">
+        <v>1024</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D31">
+        <v>128</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H31" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32">
+        <v>1024</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D32">
+        <v>256</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G32" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H32" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33">
+        <v>1024</v>
+      </c>
+      <c r="B33" s="4">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2">
+        <f t="shared" si="3"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D33" s="4">
+        <v>512</v>
+      </c>
+      <c r="E33" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0625</v>
+      </c>
+      <c r="G33" s="3" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H33" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I43" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" ht="15">
+      <c r="A44">
+        <v>256</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <f t="shared" ref="C44:C51" si="8">2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D44">
+        <f>2^0</f>
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <f t="shared" ref="E44:E51" si="9">32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F44">
+        <v>0.34131958944444402</v>
+      </c>
+      <c r="G44">
+        <f>3600*F44</f>
+        <v>1228.7505219999985</v>
+      </c>
+      <c r="H44">
+        <f>G$44/G44</f>
+        <v>1</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" s="7">
+        <v>1</v>
+      </c>
+      <c r="K44" s="8">
+        <v>2942308</v>
+      </c>
+    </row>
+    <row r="45" ht="15">
+      <c r="A45">
+        <v>256</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D45" s="2">
+        <f>2^1</f>
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F45">
+        <v>0.21012079083333299</v>
+      </c>
+      <c r="G45">
+        <f>3600*F45</f>
+        <v>756.43484699999874</v>
+      </c>
+      <c r="H45">
+        <f>G$44/G45</f>
+        <v>1.6243970341572598</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="7">
+        <v>1.99</v>
+      </c>
+      <c r="K45" s="9">
+        <v>2942265</v>
+      </c>
+    </row>
+    <row r="46" ht="15">
+      <c r="A46">
+        <v>256</v>
+      </c>
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D46" s="2">
+        <f>2^2</f>
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F46">
+        <v>0.10817702</v>
+      </c>
+      <c r="G46">
+        <f>3600*F46</f>
+        <v>389.43727200000001</v>
+      </c>
+      <c r="H46">
+        <f>G$44/G46</f>
+        <v>3.1551949706549878</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="7">
+        <v>3.98</v>
+      </c>
+      <c r="K46" s="9">
+        <v>2942232</v>
+      </c>
+    </row>
+    <row r="47" ht="15">
+      <c r="A47">
+        <v>256</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D47" s="2">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F47" s="10">
+        <v>0.061872239722222222</v>
+      </c>
+      <c r="G47">
+        <f>3600*F47</f>
+        <v>222.74006299999999</v>
+      </c>
+      <c r="H47">
+        <f>G$44/G47</f>
+        <v>5.5165222881345706</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="7">
+        <v>7.9699999999999998</v>
+      </c>
+      <c r="K47" s="9">
+        <v>2940200</v>
+      </c>
+    </row>
+    <row r="48" ht="15">
+      <c r="A48">
+        <v>256</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D48" s="2">
+        <f>2^4</f>
+        <v>16</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F48" s="10">
+        <v>0.035382613888888893</v>
+      </c>
+      <c r="G48">
+        <f>3600*F48</f>
+        <v>127.37741000000001</v>
+      </c>
+      <c r="H48">
+        <f>G$44/G48</f>
+        <v>9.6465340439878489</v>
+      </c>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="9">
+        <v>2935674</v>
+      </c>
+    </row>
+    <row r="49" ht="15">
+      <c r="A49">
+        <v>256</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D49" s="2">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F49" s="10">
+        <v>0.019179034166666671</v>
+      </c>
+      <c r="G49">
+        <f>3600*F49</f>
+        <v>69.044523000000012</v>
+      </c>
+      <c r="H49">
+        <f>G$44/G49</f>
+        <v>17.79649519774361</v>
+      </c>
+      <c r="K49" s="9">
+        <v>2935666</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50">
+        <v>256</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D50" s="2">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F50" s="10">
+        <v>0.0099714886111111102</v>
+      </c>
+      <c r="G50">
+        <f>3600*F50</f>
+        <v>35.897358999999994</v>
+      </c>
+      <c r="H50">
+        <f>G$44/G50</f>
+        <v>34.229552151733465</v>
+      </c>
+      <c r="K50" s="8">
+        <v>2935412</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51">
+        <v>256</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D51" s="2">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F51" s="10">
+        <v>0.0079847466666666672</v>
+      </c>
+      <c r="G51">
+        <f>3600*F51</f>
+        <v>28.745088000000003</v>
+      </c>
+      <c r="H51">
+        <f>G$44/G51</f>
+        <v>42.74645191554113</v>
+      </c>
+      <c r="K51" s="8">
+        <v>2935310</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="12">
+        <v>256</v>
+      </c>
+      <c r="B52" s="12">
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D52" s="12">
+        <v>256</v>
+      </c>
+      <c r="E52" s="13">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="K52" s="8"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="C53" s="2"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="K53" s="8"/>
+    </row>
+    <row r="54" ht="15">
+      <c r="A54" s="4">
+        <v>512</v>
+      </c>
+      <c r="B54" s="4">
+        <v>5</v>
+      </c>
+      <c r="C54">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D54">
+        <f>2^0</f>
+        <v>1</v>
+      </c>
+      <c r="E54" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F54">
+        <v>3.05303789083333</v>
+      </c>
+      <c r="G54">
+        <f>3600*F54</f>
+        <v>10990.936406999988</v>
+      </c>
+      <c r="H54">
+        <f>G$54/G54</f>
+        <v>1</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="7">
+        <v>1</v>
+      </c>
+      <c r="K54" s="8">
+        <v>2944950</v>
+      </c>
+    </row>
+    <row r="55" ht="15">
+      <c r="A55" s="4">
+        <v>512</v>
+      </c>
+      <c r="B55" s="4">
+        <v>5</v>
+      </c>
+      <c r="C55">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D55">
+        <f>2^1</f>
+        <v>2</v>
+      </c>
+      <c r="E55" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F55">
+        <v>2.8691363722222198</v>
+      </c>
+      <c r="G55">
+        <f>3600*F55</f>
+        <v>10328.890939999992</v>
+      </c>
+      <c r="H55">
+        <f>G$54/G55</f>
+        <v>1.0640964718134585</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="7">
+        <v>1.99</v>
+      </c>
+      <c r="K55" s="8">
+        <v>2944937</v>
+      </c>
+    </row>
+    <row r="56" ht="15">
+      <c r="A56" s="4">
+        <v>512</v>
+      </c>
+      <c r="B56" s="4">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D56">
+        <f>2^2</f>
+        <v>4</v>
+      </c>
+      <c r="E56" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F56">
+        <v>1.0865374888888899</v>
+      </c>
+      <c r="G56">
+        <f>3600*F56</f>
+        <v>3911.5349600000036</v>
+      </c>
+      <c r="H56">
+        <f>G$54/G56</f>
+        <v>2.8098780962959817</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="1">
+      <c r="J56" s="7">
+        <v>3.98</v>
+      </c>
+      <c r="K56" s="8">
+        <v>2919149</v>
+      </c>
+    </row>
+    <row r="57" ht="15">
+      <c r="A57" s="4">
+        <v>512</v>
+      </c>
+      <c r="B57" s="4">
         <v>5</v>
       </c>
-      <c r="C15">
-        <f>B15*3600</f>
-        <v>18000</v>
-      </c>
-      <c r="D15" s="3">
-        <f>C$9/C15</f>
-        <v>0.26012025416666701</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="C57">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D57">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="E57" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F57">
+        <v>0.52369764194444401</v>
+      </c>
+      <c r="G57">
+        <f>3600*F57</f>
+        <v>1885.3115109999985</v>
+      </c>
+      <c r="H57">
+        <f>G$54/G57</f>
+        <v>5.8297720789760756</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="7">
+        <v>7.9699999999999998</v>
+      </c>
+      <c r="K57" s="8">
+        <v>2927478</v>
+      </c>
+    </row>
+    <row r="58" ht="15">
+      <c r="A58" s="4">
+        <v>512</v>
+      </c>
+      <c r="B58" s="4">
+        <v>5</v>
+      </c>
+      <c r="C58">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D58">
+        <f>2^4</f>
+        <v>16</v>
+      </c>
+      <c r="E58" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F58">
+        <v>0.29082068694444402</v>
+      </c>
+      <c r="G58">
+        <f>3600*F58</f>
+        <v>1046.9544729999984</v>
+      </c>
+      <c r="H58">
+        <f>G$54/G58</f>
+        <v>10.498007974984796</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" s="7">
+        <v>15.94</v>
+      </c>
+      <c r="K58" s="8">
+        <v>2917264</v>
+      </c>
+    </row>
+    <row r="59" ht="15">
+      <c r="A59" s="4">
+        <v>512</v>
+      </c>
+      <c r="B59" s="4">
+        <v>5</v>
+      </c>
+      <c r="C59">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D59">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E59" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F59">
+        <v>0.15386960194444399</v>
+      </c>
+      <c r="G59">
+        <f>3600*F59</f>
+        <v>553.9305669999984</v>
+      </c>
+      <c r="H59">
+        <f>G$54/G59</f>
+        <v>19.841722161182016</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" s="7">
+        <v>31.870000000000001</v>
+      </c>
+      <c r="K59" s="8">
+        <v>2917262</v>
+      </c>
+    </row>
+    <row r="60" ht="15">
+      <c r="A60" s="4">
+        <v>512</v>
+      </c>
+      <c r="B60" s="4">
+        <v>5</v>
+      </c>
+      <c r="C60">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D60">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E60" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F60" s="10">
+        <v>0.094462038888888877</v>
+      </c>
+      <c r="G60">
+        <f>3600*F60</f>
+        <v>340.06333999999998</v>
+      </c>
+      <c r="H60">
+        <f>G$54/G60</f>
+        <v>32.320262475220026</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="7">
+        <v>63.710000000000001</v>
+      </c>
+      <c r="K60" s="8">
+        <v>2915598</v>
+      </c>
+    </row>
+    <row r="61" ht="15">
+      <c r="A61" s="4">
+        <v>512</v>
+      </c>
+      <c r="B61" s="4">
+        <v>5</v>
+      </c>
+      <c r="C61">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D61">
+        <f>2^7</f>
         <v>128</v>
       </c>
-      <c r="F15" s="3">
-        <v>512</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="E61" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F61" s="10">
+        <v>0.068848739722222219</v>
+      </c>
+      <c r="G61">
+        <f>3600*F61</f>
+        <v>247.85546299999999</v>
+      </c>
+      <c r="H61">
+        <f>G$54/G61</f>
+        <v>44.344136191180056</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" s="7">
+        <v>127.36</v>
+      </c>
+      <c r="K61" s="8">
+        <v>2915566</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="K62" s="8"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B63" s="4">
+        <v>5</v>
+      </c>
+      <c r="C63" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D63" s="4">
+        <f>2^0</f>
+        <v>1</v>
+      </c>
+      <c r="E63" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F63"/>
+      <c r="G63">
+        <f>3600*F63</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="8"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B64" s="4">
+        <v>5</v>
+      </c>
+      <c r="C64" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D64" s="4">
+        <f>2^1</f>
+        <v>2</v>
+      </c>
+      <c r="E64" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F64"/>
+      <c r="G64">
+        <f>3600*F64</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" s="8"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B65" s="4">
+        <v>5</v>
+      </c>
+      <c r="C65" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D65" s="4">
+        <f>2^2</f>
+        <v>4</v>
+      </c>
+      <c r="E65" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F65"/>
+      <c r="G65">
+        <f>3600*F65</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="8">
+        <v>2968238</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B66" s="4">
+        <v>5</v>
+      </c>
+      <c r="C66" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D66" s="4">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="E66" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F66">
+        <v>5.01026725944444</v>
+      </c>
+      <c r="G66">
+        <f>3600*F66</f>
+        <v>18036.962133999983</v>
+      </c>
+      <c r="I66" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>11</v>
+      <c r="J66" s="7">
+        <v>7.9699999999999998</v>
+      </c>
+      <c r="K66" s="8">
+        <v>2887572</v>
       </c>
     </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B67" s="4">
+        <v>5</v>
+      </c>
+      <c r="C67" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D67" s="4">
+        <f>2^4</f>
+        <v>16</v>
+      </c>
+      <c r="E67" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F67">
+        <v>3.2392529866666702</v>
+      </c>
+      <c r="G67">
+        <f>3600*F67</f>
+        <v>11661.310752000012</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" s="7">
+        <v>15.94</v>
+      </c>
+      <c r="K67" s="8">
+        <v>2887528</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B68" s="4">
+        <v>5</v>
+      </c>
+      <c r="C68" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D68" s="4">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E68" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F68">
+        <v>1.39384133694444</v>
+      </c>
+      <c r="G68">
+        <f>3600*F68</f>
+        <v>5017.8288129999837</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="7">
+        <v>31.870000000000001</v>
+      </c>
+      <c r="K68" s="8">
+        <v>2863616</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B69" s="4">
+        <v>5</v>
+      </c>
+      <c r="C69" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D69" s="4">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E69" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F69">
+        <v>0.88665442194444399</v>
+      </c>
+      <c r="G69">
+        <f>3600*F69</f>
+        <v>3191.9559189999982</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="7">
+        <v>63.710000000000001</v>
+      </c>
+      <c r="K69" s="8">
+        <v>2862265</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B70" s="4">
+        <v>5</v>
+      </c>
+      <c r="C70" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D70" s="4">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E70" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F70">
+        <v>0.63989486638888904</v>
+      </c>
+      <c r="G70">
+        <f>3600*F70</f>
+        <v>2303.6215190000007</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="7">
+        <v>127.31</v>
+      </c>
+      <c r="K70" s="8">
+        <v>2859759</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/testResults/compilerResults/CompilerResults.xlsx
+++ b/testResults/compilerResults/CompilerResults.xlsx
@@ -115,7 +115,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -129,16 +129,11 @@
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,7 +164,6 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -181,12 +175,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
@@ -965,7 +960,16 @@
               <c:f>Sheet1!$H$44:$H$51</c:f>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
         </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
         <c:axId val="2140841497"/>
         <c:axId val="2140841498"/>
       </c:scatterChart>
@@ -1032,6 +1036,7 @@
         </c:txPr>
         <c:crossAx val="2140841498"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="2140841498"/>
@@ -1148,8 +1153,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm>
-      <a:off x="7962899" y="7215187"/>
-      <a:ext cx="4552949" cy="2724149"/>
+      <a:off x="7962898" y="7215186"/>
+      <a:ext cx="4552949" cy="2905124"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -1278,15 +1283,24 @@
           </c:marker>
           <c:xVal>
             <c:strRef>
-              <c:f>Sheet1!$D$54:$D$61</c:f>
+              <c:f>Sheet1!$D$55:$D$62</c:f>
             </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$54:$H$61</c:f>
+              <c:f>Sheet1!$H$55:$H$62</c:f>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
         </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
         <c:axId val="2140841503"/>
         <c:axId val="2140841504"/>
       </c:scatterChart>
@@ -1353,6 +1367,7 @@
         </c:txPr>
         <c:crossAx val="2140841504"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="2140841504"/>
@@ -1469,8 +1484,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm>
-      <a:off x="8229599" y="10120312"/>
-      <a:ext cx="4552949" cy="2724149"/>
+      <a:off x="8229598" y="10301286"/>
+      <a:ext cx="4552949" cy="3105149"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -3921,15 +3936,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:colOff>380998</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:rowOff>157161</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:colOff>57148</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>109536</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3939,8 +3954,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7962899" y="7215187"/>
-        <a:ext cx="4552949" cy="2724149"/>
+        <a:off x="7962898" y="7215186"/>
+        <a:ext cx="4552949" cy="2905124"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3953,15 +3968,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>38099</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:colOff>38098</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>100011</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>323849</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:colOff>323848</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3971,8 +3986,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8229599" y="10120312"/>
-        <a:ext cx="4552949" cy="2724149"/>
+        <a:off x="8229598" y="10301286"/>
+        <a:ext cx="4552949" cy="3105149"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5404,7 +5419,7 @@
       <c r="E43" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -5419,7 +5434,7 @@
       <c r="J43" t="s">
         <v>13</v>
       </c>
-      <c r="K43" s="6" t="s">
+      <c r="K43" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5431,7 +5446,7 @@
         <v>5</v>
       </c>
       <c r="C44">
-        <f t="shared" ref="C44:C51" si="8">2^-5</f>
+        <f t="shared" ref="C44:C52" si="8">2^-5</f>
         <v>0.03125</v>
       </c>
       <c r="D44">
@@ -5439,27 +5454,27 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <f t="shared" ref="E44:E51" si="9">32/256</f>
+        <f t="shared" ref="E44:E52" si="9">32/256</f>
         <v>0.125</v>
       </c>
       <c r="F44">
         <v>0.34131958944444402</v>
       </c>
       <c r="G44">
-        <f>3600*F44</f>
+        <f t="shared" ref="G44:G73" si="10">3600*F44</f>
         <v>1228.7505219999985</v>
       </c>
       <c r="H44">
-        <f>G$44/G44</f>
+        <f t="shared" ref="H44:H51" si="11">G$44/G44</f>
         <v>1</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J44" s="7">
+      <c r="J44" s="6">
         <v>1</v>
       </c>
-      <c r="K44" s="8">
+      <c r="K44" s="7">
         <v>2942308</v>
       </c>
     </row>
@@ -5486,20 +5501,20 @@
         <v>0.21012079083333299</v>
       </c>
       <c r="G45">
-        <f>3600*F45</f>
+        <f t="shared" si="10"/>
         <v>756.43484699999874</v>
       </c>
       <c r="H45">
-        <f>G$44/G45</f>
+        <f t="shared" si="11"/>
         <v>1.6243970341572598</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I45" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J45" s="7">
+      <c r="J45" s="6">
         <v>1.99</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="8">
         <v>2942265</v>
       </c>
     </row>
@@ -5526,20 +5541,20 @@
         <v>0.10817702</v>
       </c>
       <c r="G46">
-        <f>3600*F46</f>
+        <f t="shared" si="10"/>
         <v>389.43727200000001</v>
       </c>
       <c r="H46">
-        <f>G$44/G46</f>
+        <f t="shared" si="11"/>
         <v>3.1551949706549878</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="I46" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J46" s="7">
+      <c r="J46" s="6">
         <v>3.98</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="8">
         <v>2942232</v>
       </c>
     </row>
@@ -5562,24 +5577,24 @@
         <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="9">
         <v>0.061872239722222222</v>
       </c>
       <c r="G47">
-        <f>3600*F47</f>
+        <f t="shared" si="10"/>
         <v>222.74006299999999</v>
       </c>
       <c r="H47">
-        <f>G$44/G47</f>
+        <f t="shared" si="11"/>
         <v>5.5165222881345706</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="I47" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J47" s="7">
+      <c r="J47" s="6">
         <v>7.9699999999999998</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="8">
         <v>2940200</v>
       </c>
     </row>
@@ -5602,20 +5617,20 @@
         <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="9">
         <v>0.035382613888888893</v>
       </c>
       <c r="G48">
-        <f>3600*F48</f>
+        <f t="shared" si="10"/>
         <v>127.37741000000001</v>
       </c>
       <c r="H48">
-        <f>G$44/G48</f>
+        <f t="shared" si="11"/>
         <v>9.6465340439878489</v>
       </c>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="9">
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="8">
         <v>2935674</v>
       </c>
     </row>
@@ -5638,18 +5653,18 @@
         <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="9">
         <v>0.019179034166666671</v>
       </c>
       <c r="G49">
-        <f>3600*F49</f>
+        <f t="shared" si="10"/>
         <v>69.044523000000012</v>
       </c>
       <c r="H49">
-        <f>G$44/G49</f>
+        <f t="shared" si="11"/>
         <v>17.79649519774361</v>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="8">
         <v>2935666</v>
       </c>
     </row>
@@ -5672,18 +5687,18 @@
         <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="9">
         <v>0.0099714886111111102</v>
       </c>
       <c r="G50">
-        <f>3600*F50</f>
+        <f t="shared" si="10"/>
         <v>35.897358999999994</v>
       </c>
       <c r="H50">
-        <f>G$44/G50</f>
+        <f t="shared" si="11"/>
         <v>34.229552151733465</v>
       </c>
-      <c r="K50" s="8">
+      <c r="K50" s="7">
         <v>2935412</v>
       </c>
     </row>
@@ -5706,7 +5721,7 @@
         <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="9">
         <v>0.0079847466666666672</v>
       </c>
       <c r="G51">
@@ -5714,81 +5729,84 @@
         <v>28.745088000000003</v>
       </c>
       <c r="H51">
-        <f>G$44/G51</f>
+        <f t="shared" si="11"/>
         <v>42.74645191554113</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="7">
         <v>2935310</v>
       </c>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="12">
+      <c r="A52" s="2">
         <v>256</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="2">
         <v>5</v>
       </c>
       <c r="C52">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D52" s="2">
+        <v>256</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0.0081580863888888883</v>
+      </c>
+      <c r="G52">
+        <f>3600*F52</f>
+        <v>29.369110999999997</v>
+      </c>
+      <c r="H52">
+        <f>G$44/G52</f>
+        <v>41.838192582676356</v>
+      </c>
+      <c r="K52" s="7">
+        <v>2980608</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="10">
+        <v>256</v>
+      </c>
+      <c r="B53" s="10">
+        <v>5</v>
+      </c>
+      <c r="C53" s="11">
         <f>2^-5</f>
         <v>0.03125</v>
       </c>
-      <c r="D52" s="12">
-        <v>256</v>
-      </c>
-      <c r="E52" s="13">
+      <c r="D53" s="10">
+        <v>512</v>
+      </c>
+      <c r="E53" s="11">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F52" s="10"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="K52" s="8"/>
-    </row>
-    <row r="53" ht="14.25">
-      <c r="C53" s="2"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="K53" s="8"/>
-    </row>
-    <row r="54" ht="15">
-      <c r="A54" s="4">
-        <v>512</v>
-      </c>
-      <c r="B54" s="4">
-        <v>5</v>
-      </c>
-      <c r="C54">
-        <f>2^-5</f>
-        <v>0.03125</v>
-      </c>
-      <c r="D54">
-        <f>2^0</f>
-        <v>1</v>
-      </c>
-      <c r="E54" s="4">
-        <f>32/256</f>
-        <v>0.125</v>
-      </c>
-      <c r="F54">
-        <v>3.05303789083333</v>
-      </c>
-      <c r="G54">
-        <f>3600*F54</f>
-        <v>10990.936406999988</v>
-      </c>
-      <c r="H54">
-        <f>G$54/G54</f>
-        <v>1</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="7">
-        <v>1</v>
-      </c>
-      <c r="K54" s="8">
-        <v>2944950</v>
-      </c>
+      <c r="F53" s="12">
+        <v>0.0313366775</v>
+      </c>
+      <c r="G53">
+        <f>3600*F53</f>
+        <v>112.812039</v>
+      </c>
+      <c r="H53">
+        <f>G$44/G53</f>
+        <v>10.892015895572976</v>
+      </c>
+      <c r="K53" s="7">
+        <v>2980673</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="C54" s="2"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="K54" s="7"/>
     </row>
     <row r="55" ht="15">
       <c r="A55" s="4">
@@ -5802,32 +5820,32 @@
         <v>0.03125</v>
       </c>
       <c r="D55">
-        <f>2^1</f>
-        <v>2</v>
+        <f>2^0</f>
+        <v>1</v>
       </c>
       <c r="E55" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F55">
-        <v>2.8691363722222198</v>
+        <v>3.05303789083333</v>
       </c>
       <c r="G55">
-        <f>3600*F55</f>
-        <v>10328.890939999992</v>
+        <f t="shared" si="10"/>
+        <v>10990.936406999988</v>
       </c>
       <c r="H55">
-        <f>G$54/G55</f>
-        <v>1.0640964718134585</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="7">
-        <v>1.99</v>
-      </c>
-      <c r="K55" s="8">
-        <v>2944937</v>
+        <f>G$55/G55</f>
+        <v>1</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="6">
+        <v>1</v>
+      </c>
+      <c r="K55" s="7">
+        <v>2944950</v>
       </c>
     </row>
     <row r="56" ht="15">
@@ -5842,32 +5860,32 @@
         <v>0.03125</v>
       </c>
       <c r="D56">
-        <f>2^2</f>
-        <v>4</v>
+        <f>2^1</f>
+        <v>2</v>
       </c>
       <c r="E56" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F56">
-        <v>1.0865374888888899</v>
+        <v>2.8691363722222198</v>
       </c>
       <c r="G56">
-        <f>3600*F56</f>
-        <v>3911.5349600000036</v>
+        <f t="shared" si="10"/>
+        <v>10328.890939999992</v>
       </c>
       <c r="H56">
-        <f>G$54/G56</f>
-        <v>2.8098780962959817</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J56" s="7">
-        <v>3.98</v>
-      </c>
-      <c r="K56" s="8">
-        <v>2919149</v>
+        <f>G$55/G56</f>
+        <v>1.0640964718134585</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="K56" s="7">
+        <v>2944937</v>
       </c>
     </row>
     <row r="57" ht="15">
@@ -5882,32 +5900,32 @@
         <v>0.03125</v>
       </c>
       <c r="D57">
-        <f>2^3</f>
-        <v>8</v>
+        <f>2^2</f>
+        <v>4</v>
       </c>
       <c r="E57" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F57">
-        <v>0.52369764194444401</v>
+        <v>1.0865374888888899</v>
       </c>
       <c r="G57">
-        <f>3600*F57</f>
-        <v>1885.3115109999985</v>
+        <f t="shared" si="10"/>
+        <v>3911.5349600000036</v>
       </c>
       <c r="H57">
-        <f>G$54/G57</f>
-        <v>5.8297720789760756</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J57" s="7">
-        <v>7.9699999999999998</v>
-      </c>
-      <c r="K57" s="8">
-        <v>2927478</v>
+        <f>G$55/G57</f>
+        <v>2.8098780962959817</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="6">
+        <v>3.98</v>
+      </c>
+      <c r="K57" s="7">
+        <v>2919149</v>
       </c>
     </row>
     <row r="58" ht="15">
@@ -5922,32 +5940,32 @@
         <v>0.03125</v>
       </c>
       <c r="D58">
-        <f>2^4</f>
-        <v>16</v>
+        <f>2^3</f>
+        <v>8</v>
       </c>
       <c r="E58" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F58">
-        <v>0.29082068694444402</v>
+        <v>0.52369764194444401</v>
       </c>
       <c r="G58">
-        <f>3600*F58</f>
-        <v>1046.9544729999984</v>
+        <f t="shared" si="10"/>
+        <v>1885.3115109999985</v>
       </c>
       <c r="H58">
-        <f>G$54/G58</f>
-        <v>10.498007974984796</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J58" s="7">
-        <v>15.94</v>
-      </c>
-      <c r="K58" s="8">
-        <v>2917264</v>
+        <f>G$55/G58</f>
+        <v>5.8297720789760756</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="6">
+        <v>7.9699999999999998</v>
+      </c>
+      <c r="K58" s="7">
+        <v>2927478</v>
       </c>
     </row>
     <row r="59" ht="15">
@@ -5962,32 +5980,32 @@
         <v>0.03125</v>
       </c>
       <c r="D59">
-        <f>2^5</f>
-        <v>32</v>
+        <f>2^4</f>
+        <v>16</v>
       </c>
       <c r="E59" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F59">
-        <v>0.15386960194444399</v>
+        <v>0.29082068694444402</v>
       </c>
       <c r="G59">
-        <f>3600*F59</f>
-        <v>553.9305669999984</v>
+        <f t="shared" si="10"/>
+        <v>1046.9544729999984</v>
       </c>
       <c r="H59">
-        <f>G$54/G59</f>
-        <v>19.841722161182016</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" s="7">
-        <v>31.870000000000001</v>
-      </c>
-      <c r="K59" s="8">
-        <v>2917262</v>
+        <f>G$55/G59</f>
+        <v>10.498007974984796</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" s="6">
+        <v>15.94</v>
+      </c>
+      <c r="K59" s="7">
+        <v>2917264</v>
       </c>
     </row>
     <row r="60" ht="15">
@@ -6002,32 +6020,32 @@
         <v>0.03125</v>
       </c>
       <c r="D60">
-        <f>2^6</f>
-        <v>64</v>
+        <f>2^5</f>
+        <v>32</v>
       </c>
       <c r="E60" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F60" s="10">
-        <v>0.094462038888888877</v>
+      <c r="F60">
+        <v>0.15386960194444399</v>
       </c>
       <c r="G60">
-        <f>3600*F60</f>
-        <v>340.06333999999998</v>
+        <f t="shared" si="10"/>
+        <v>553.9305669999984</v>
       </c>
       <c r="H60">
-        <f>G$54/G60</f>
-        <v>32.320262475220026</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" s="7">
-        <v>63.710000000000001</v>
-      </c>
-      <c r="K60" s="8">
-        <v>2915598</v>
+        <f>G$55/G60</f>
+        <v>19.841722161182016</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" s="6">
+        <v>31.870000000000001</v>
+      </c>
+      <c r="K60" s="7">
+        <v>2917262</v>
       </c>
     </row>
     <row r="61" ht="15">
@@ -6042,121 +6060,146 @@
         <v>0.03125</v>
       </c>
       <c r="D61">
-        <f>2^7</f>
-        <v>128</v>
+        <f>2^6</f>
+        <v>64</v>
       </c>
       <c r="E61" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F61" s="10">
-        <v>0.068848739722222219</v>
+      <c r="F61" s="9">
+        <v>0.094462038888888877</v>
       </c>
       <c r="G61">
-        <f>3600*F61</f>
-        <v>247.85546299999999</v>
+        <f t="shared" si="10"/>
+        <v>340.06333999999998</v>
       </c>
       <c r="H61">
-        <f>G$54/G61</f>
-        <v>44.344136191180056</v>
-      </c>
-      <c r="I61" s="7" t="s">
+        <f>G$55/G61</f>
+        <v>32.320262475220026</v>
+      </c>
+      <c r="I61" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="7">
-        <v>127.36</v>
-      </c>
-      <c r="K61" s="8">
-        <v>2915566</v>
-      </c>
-    </row>
-    <row r="62" ht="14.25">
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="K62" s="8"/>
-    </row>
-    <row r="63" ht="14.25">
-      <c r="A63" s="4">
-        <v>1024</v>
-      </c>
-      <c r="B63" s="4">
+      <c r="J61" s="6">
+        <v>63.710000000000001</v>
+      </c>
+      <c r="K61" s="7">
+        <v>2915598</v>
+      </c>
+    </row>
+    <row r="62" ht="15">
+      <c r="A62" s="4">
+        <v>512</v>
+      </c>
+      <c r="B62" s="4">
         <v>5</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C62">
         <f>2^-5</f>
         <v>0.03125</v>
       </c>
-      <c r="D63" s="4">
-        <f>2^0</f>
-        <v>1</v>
-      </c>
-      <c r="E63" s="4">
+      <c r="D62">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E62" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F63"/>
+      <c r="F62" s="9">
+        <v>0.068848739722222219</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="10"/>
+        <v>247.85546299999999</v>
+      </c>
+      <c r="H62">
+        <f>G$55/G62</f>
+        <v>44.344136191180056</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="6">
+        <v>127.36</v>
+      </c>
+      <c r="K62" s="7">
+        <v>2915566</v>
+      </c>
+    </row>
+    <row r="63" ht="15">
+      <c r="A63" s="11">
+        <v>512</v>
+      </c>
+      <c r="B63" s="11">
+        <v>5</v>
+      </c>
+      <c r="C63" s="11">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D63" s="10">
+        <v>256</v>
+      </c>
+      <c r="E63" s="11">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F63" s="12">
+        <v>0.076658587777777773</v>
+      </c>
       <c r="G63">
         <f>3600*F63</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="8"/>
-    </row>
-    <row r="64" ht="14.25">
-      <c r="A64" s="4">
-        <v>1024</v>
-      </c>
-      <c r="B64" s="4">
+        <v>275.97091599999999</v>
+      </c>
+      <c r="H63">
+        <f>G$55/G63</f>
+        <v>39.82643014092104</v>
+      </c>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="7">
+        <v>2981053</v>
+      </c>
+    </row>
+    <row r="64" ht="15">
+      <c r="A64" s="11">
+        <v>512</v>
+      </c>
+      <c r="B64" s="11">
         <v>5</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="11">
         <f>2^-5</f>
         <v>0.03125</v>
       </c>
-      <c r="D64" s="4">
-        <f>2^1</f>
-        <v>2</v>
-      </c>
-      <c r="E64" s="4">
+      <c r="D64" s="10">
+        <v>512</v>
+      </c>
+      <c r="E64" s="11">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F64"/>
+      <c r="F64" s="12">
+        <v>0.074688044166666662</v>
+      </c>
       <c r="G64">
         <f>3600*F64</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K64" s="8"/>
+        <v>268.876959</v>
+      </c>
+      <c r="H64">
+        <f>G$55/G64</f>
+        <v>40.877196944941602</v>
+      </c>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="7"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="4">
-        <v>1024</v>
-      </c>
-      <c r="B65" s="4">
-        <v>5</v>
-      </c>
-      <c r="C65" s="4">
-        <f>2^-5</f>
-        <v>0.03125</v>
-      </c>
-      <c r="D65" s="4">
-        <f>2^2</f>
-        <v>4</v>
-      </c>
-      <c r="E65" s="4">
-        <f>32/256</f>
-        <v>0.125</v>
-      </c>
       <c r="F65"/>
-      <c r="G65">
-        <f>3600*F65</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="8">
-        <v>2968238</v>
-      </c>
+      <c r="G65"/>
+      <c r="K65" s="7"/>
     </row>
     <row r="66" ht="14.25">
       <c r="A66" s="4">
@@ -6170,29 +6213,19 @@
         <v>0.03125</v>
       </c>
       <c r="D66" s="4">
-        <f>2^3</f>
-        <v>8</v>
+        <f>2^0</f>
+        <v>1</v>
       </c>
       <c r="E66" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F66">
-        <v>5.01026725944444</v>
-      </c>
+      <c r="F66"/>
       <c r="G66">
-        <f>3600*F66</f>
-        <v>18036.962133999983</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J66" s="7">
-        <v>7.9699999999999998</v>
-      </c>
-      <c r="K66" s="8">
-        <v>2887572</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K66" s="7"/>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="4">
@@ -6206,29 +6239,22 @@
         <v>0.03125</v>
       </c>
       <c r="D67" s="4">
-        <f>2^4</f>
-        <v>16</v>
+        <f>2^1</f>
+        <v>2</v>
       </c>
       <c r="E67" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F67">
-        <v>3.2392529866666702</v>
-      </c>
+      <c r="F67"/>
       <c r="G67">
-        <f>3600*F67</f>
-        <v>11661.310752000012</v>
-      </c>
-      <c r="I67" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" s="7">
-        <v>15.94</v>
-      </c>
-      <c r="K67" s="8">
-        <v>2887528</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K67" s="7"/>
     </row>
     <row r="68" ht="14.25">
       <c r="A68" s="4">
@@ -6242,28 +6268,20 @@
         <v>0.03125</v>
       </c>
       <c r="D68" s="4">
-        <f>2^5</f>
-        <v>32</v>
+        <f>2^2</f>
+        <v>4</v>
       </c>
       <c r="E68" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
-      <c r="F68">
-        <v>1.39384133694444</v>
-      </c>
+      <c r="F68"/>
       <c r="G68">
-        <f>3600*F68</f>
-        <v>5017.8288129999837</v>
-      </c>
-      <c r="I68" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J68" s="7">
-        <v>31.870000000000001</v>
-      </c>
-      <c r="K68" s="8">
-        <v>2863616</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="7">
+        <v>2968238</v>
       </c>
     </row>
     <row r="69" ht="14.25">
@@ -6278,28 +6296,28 @@
         <v>0.03125</v>
       </c>
       <c r="D69" s="4">
-        <f>2^6</f>
-        <v>64</v>
+        <f>2^3</f>
+        <v>8</v>
       </c>
       <c r="E69" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F69">
-        <v>0.88665442194444399</v>
+        <v>5.01026725944444</v>
       </c>
       <c r="G69">
-        <f>3600*F69</f>
-        <v>3191.9559189999982</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J69" s="7">
-        <v>63.710000000000001</v>
-      </c>
-      <c r="K69" s="8">
-        <v>2862265</v>
+        <f t="shared" si="10"/>
+        <v>18036.962133999983</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="6">
+        <v>7.9699999999999998</v>
+      </c>
+      <c r="K69" s="7">
+        <v>2887572</v>
       </c>
     </row>
     <row r="70" ht="14.25">
@@ -6314,31 +6332,196 @@
         <v>0.03125</v>
       </c>
       <c r="D70" s="4">
-        <f>2^7</f>
-        <v>128</v>
+        <f>2^4</f>
+        <v>16</v>
       </c>
       <c r="E70" s="4">
         <f>32/256</f>
         <v>0.125</v>
       </c>
       <c r="F70">
+        <v>3.2392529866666702</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="10"/>
+        <v>11661.310752000012</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" s="6">
+        <v>15.94</v>
+      </c>
+      <c r="K70" s="7">
+        <v>2887528</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B71" s="4">
+        <v>5</v>
+      </c>
+      <c r="C71" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D71" s="4">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E71" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F71">
+        <v>1.39384133694444</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="10"/>
+        <v>5017.8288129999837</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="6">
+        <v>31.870000000000001</v>
+      </c>
+      <c r="K71" s="7">
+        <v>2863616</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="A72" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B72" s="4">
+        <v>5</v>
+      </c>
+      <c r="C72" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D72" s="4">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E72" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F72">
+        <v>0.88665442194444399</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="10"/>
+        <v>3191.9559189999982</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" s="6">
+        <v>63.710000000000001</v>
+      </c>
+      <c r="K72" s="7">
+        <v>2862265</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="A73" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B73" s="4">
+        <v>5</v>
+      </c>
+      <c r="C73" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D73" s="4">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E73" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F73">
         <v>0.63989486638888904</v>
       </c>
-      <c r="G70">
-        <f>3600*F70</f>
+      <c r="G73">
+        <f t="shared" si="10"/>
         <v>2303.6215190000007</v>
       </c>
-      <c r="I70" s="7" t="s">
+      <c r="I73" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J70" s="7">
+      <c r="J73" s="6">
         <v>127.31</v>
       </c>
-      <c r="K70" s="8">
+      <c r="K73" s="7">
         <v>2859759</v>
       </c>
     </row>
-    <row r="72" ht="14.25"/>
+    <row r="74" ht="14.25">
+      <c r="A74">
+        <v>1024</v>
+      </c>
+      <c r="B74">
+        <v>5</v>
+      </c>
+      <c r="C74" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D74">
+        <v>256</v>
+      </c>
+      <c r="E74" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F74">
+        <v>0.74468592027777802</v>
+      </c>
+      <c r="G74">
+        <f>3600*F74</f>
+        <v>2680.8693130000011</v>
+      </c>
+      <c r="K74">
+        <v>2981373</v>
+      </c>
+    </row>
+    <row r="75" ht="14.25">
+      <c r="A75">
+        <v>1024</v>
+      </c>
+      <c r="B75">
+        <v>5</v>
+      </c>
+      <c r="C75" s="4">
+        <f>2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D75">
+        <v>512</v>
+      </c>
+      <c r="E75" s="4">
+        <f>32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F75">
+        <v>0.57972249638888895</v>
+      </c>
+      <c r="G75">
+        <f>3600*F75</f>
+        <v>2087.0009870000004</v>
+      </c>
+      <c r="K75">
+        <v>2982462</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/testResults/compilerResults/CompilerResults.xlsx
+++ b/testResults/compilerResults/CompilerResults.xlsx
@@ -156,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
@@ -175,14 +175,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -965,6 +957,7 @@
         <c:dLbls>
           <c:showBubbleSize val="0"/>
           <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
           <c:showLegendKey val="0"/>
           <c:showPercent val="0"/>
           <c:showSerName val="0"/>
@@ -1296,6 +1289,7 @@
         <c:dLbls>
           <c:showBubbleSize val="0"/>
           <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
           <c:showLegendKey val="0"/>
           <c:showPercent val="0"/>
           <c:showSerName val="0"/>
@@ -3970,13 +3964,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>38098</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>100011</xdr:rowOff>
+      <xdr:rowOff>100010</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>323848</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>4761</xdr:rowOff>
+      <xdr:rowOff>4760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5446,7 +5440,7 @@
         <v>5</v>
       </c>
       <c r="C44">
-        <f t="shared" ref="C44:C52" si="8">2^-5</f>
+        <f t="shared" ref="C44:C75" si="8">2^-5</f>
         <v>0.03125</v>
       </c>
       <c r="D44">
@@ -5454,18 +5448,18 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <f t="shared" ref="E44:E52" si="9">32/256</f>
+        <f t="shared" ref="E44:E75" si="9">32/256</f>
         <v>0.125</v>
       </c>
       <c r="F44">
         <v>0.34131958944444402</v>
       </c>
       <c r="G44">
-        <f t="shared" ref="G44:G73" si="10">3600*F44</f>
+        <f t="shared" ref="G44:G75" si="10">3600*F44</f>
         <v>1228.7505219999985</v>
       </c>
       <c r="H44">
-        <f t="shared" ref="H44:H51" si="11">G$44/G44</f>
+        <f t="shared" ref="H44:H53" si="11">G$44/G44</f>
         <v>1</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -5725,7 +5719,7 @@
         <v>0.0079847466666666672</v>
       </c>
       <c r="G51">
-        <f>3600*F51</f>
+        <f t="shared" si="10"/>
         <v>28.745088000000003</v>
       </c>
       <c r="H51">
@@ -5755,52 +5749,48 @@
         <v>0.125</v>
       </c>
       <c r="F52" s="9">
-        <v>0.0081580863888888883</v>
+        <v>0.0083248658333333336</v>
       </c>
       <c r="G52">
-        <f>3600*F52</f>
-        <v>29.369110999999997</v>
+        <f t="shared" si="10"/>
+        <v>29.969517</v>
       </c>
       <c r="H52">
-        <f>G$44/G52</f>
-        <v>41.838192582676356</v>
-      </c>
-      <c r="K52" s="7">
-        <v>2980608</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>41.000010844352225</v>
+      </c>
+      <c r="K52" s="7"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="10">
+      <c r="A53" s="2">
         <v>256</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="2">
         <v>5</v>
       </c>
-      <c r="C53" s="11">
-        <f>2^-5</f>
+      <c r="C53" s="4">
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="2">
         <v>512</v>
       </c>
-      <c r="E53" s="11">
-        <f>32/256</f>
+      <c r="E53" s="4">
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F53" s="12">
-        <v>0.0313366775</v>
+      <c r="F53" s="9">
+        <v>0.034152586111111112</v>
       </c>
       <c r="G53">
-        <f>3600*F53</f>
-        <v>112.812039</v>
+        <f t="shared" si="10"/>
+        <v>122.94931</v>
       </c>
       <c r="H53">
-        <f>G$44/G53</f>
-        <v>10.892015895572976</v>
-      </c>
-      <c r="K53" s="7">
-        <v>2980673</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>9.9939602914404198</v>
+      </c>
+      <c r="K53" s="7"/>
     </row>
     <row r="54" ht="14.25">
       <c r="C54" s="2"/>
@@ -5816,7 +5806,7 @@
         <v>5</v>
       </c>
       <c r="C55">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D55">
@@ -5824,7 +5814,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F55">
@@ -5835,7 +5825,7 @@
         <v>10990.936406999988</v>
       </c>
       <c r="H55">
-        <f>G$55/G55</f>
+        <f t="shared" ref="H55:H64" si="12">G$55/G55</f>
         <v>1</v>
       </c>
       <c r="I55" s="6" t="s">
@@ -5856,7 +5846,7 @@
         <v>5</v>
       </c>
       <c r="C56">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D56">
@@ -5864,7 +5854,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F56">
@@ -5875,7 +5865,7 @@
         <v>10328.890939999992</v>
       </c>
       <c r="H56">
-        <f>G$55/G56</f>
+        <f t="shared" si="12"/>
         <v>1.0640964718134585</v>
       </c>
       <c r="I56" s="6" t="s">
@@ -5896,7 +5886,7 @@
         <v>5</v>
       </c>
       <c r="C57">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D57">
@@ -5904,7 +5894,7 @@
         <v>4</v>
       </c>
       <c r="E57" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F57">
@@ -5915,7 +5905,7 @@
         <v>3911.5349600000036</v>
       </c>
       <c r="H57">
-        <f>G$55/G57</f>
+        <f t="shared" si="12"/>
         <v>2.8098780962959817</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -5936,7 +5926,7 @@
         <v>5</v>
       </c>
       <c r="C58">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D58">
@@ -5944,7 +5934,7 @@
         <v>8</v>
       </c>
       <c r="E58" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F58">
@@ -5955,7 +5945,7 @@
         <v>1885.3115109999985</v>
       </c>
       <c r="H58">
-        <f>G$55/G58</f>
+        <f t="shared" si="12"/>
         <v>5.8297720789760756</v>
       </c>
       <c r="I58" s="6" t="s">
@@ -5976,7 +5966,7 @@
         <v>5</v>
       </c>
       <c r="C59">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D59">
@@ -5984,7 +5974,7 @@
         <v>16</v>
       </c>
       <c r="E59" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F59">
@@ -5995,7 +5985,7 @@
         <v>1046.9544729999984</v>
       </c>
       <c r="H59">
-        <f>G$55/G59</f>
+        <f t="shared" si="12"/>
         <v>10.498007974984796</v>
       </c>
       <c r="I59" s="6" t="s">
@@ -6016,7 +6006,7 @@
         <v>5</v>
       </c>
       <c r="C60">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D60">
@@ -6024,7 +6014,7 @@
         <v>32</v>
       </c>
       <c r="E60" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F60">
@@ -6035,7 +6025,7 @@
         <v>553.9305669999984</v>
       </c>
       <c r="H60">
-        <f>G$55/G60</f>
+        <f t="shared" si="12"/>
         <v>19.841722161182016</v>
       </c>
       <c r="I60" s="6" t="s">
@@ -6056,7 +6046,7 @@
         <v>5</v>
       </c>
       <c r="C61">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D61">
@@ -6064,7 +6054,7 @@
         <v>64</v>
       </c>
       <c r="E61" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F61" s="9">
@@ -6075,7 +6065,7 @@
         <v>340.06333999999998</v>
       </c>
       <c r="H61">
-        <f>G$55/G61</f>
+        <f t="shared" si="12"/>
         <v>32.320262475220026</v>
       </c>
       <c r="I61" s="6" t="s">
@@ -6096,7 +6086,7 @@
         <v>5</v>
       </c>
       <c r="C62">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D62">
@@ -6104,7 +6094,7 @@
         <v>128</v>
       </c>
       <c r="E62" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F62" s="9">
@@ -6115,7 +6105,7 @@
         <v>247.85546299999999</v>
       </c>
       <c r="H62">
-        <f>G$55/G62</f>
+        <f t="shared" si="12"/>
         <v>44.344136191180056</v>
       </c>
       <c r="I62" s="6" t="s">
@@ -6129,71 +6119,73 @@
       </c>
     </row>
     <row r="63" ht="15">
-      <c r="A63" s="11">
+      <c r="A63" s="4">
         <v>512</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="4">
         <v>5</v>
       </c>
-      <c r="C63" s="11">
-        <f>2^-5</f>
+      <c r="C63" s="4">
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="2">
         <v>256</v>
       </c>
-      <c r="E63" s="11">
-        <f>32/256</f>
+      <c r="E63" s="4">
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F63" s="12">
-        <v>0.076658587777777773</v>
+      <c r="F63" s="9">
+        <f>2*0.0333151991666667</f>
+        <v>0.066630398333333396</v>
       </c>
       <c r="G63">
-        <f>3600*F63</f>
-        <v>275.97091599999999</v>
+        <f t="shared" si="10"/>
+        <v>239.86943400000024</v>
       </c>
       <c r="H63">
-        <f>G$55/G63</f>
-        <v>39.82643014092104</v>
-      </c>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
+        <f t="shared" si="12"/>
+        <v>45.820495857758921</v>
+      </c>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
       <c r="K63" s="7">
-        <v>2981053</v>
+        <v>3087445</v>
       </c>
     </row>
     <row r="64" ht="15">
-      <c r="A64" s="11">
+      <c r="A64" s="4">
         <v>512</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="4">
         <v>5</v>
       </c>
-      <c r="C64" s="11">
-        <f>2^-5</f>
+      <c r="C64" s="4">
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="2">
         <v>512</v>
       </c>
-      <c r="E64" s="11">
-        <f>32/256</f>
+      <c r="E64" s="4">
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F64" s="12">
-        <v>0.074688044166666662</v>
+      <c r="F64" s="9">
+        <f>2*0.03618602805555556</f>
+        <v>0.072372056111111124</v>
       </c>
       <c r="G64">
-        <f>3600*F64</f>
-        <v>268.876959</v>
+        <f t="shared" si="10"/>
+        <v>260.53940200000005</v>
       </c>
       <c r="H64">
-        <f>G$55/G64</f>
-        <v>40.877196944941602</v>
-      </c>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
+        <f t="shared" si="12"/>
+        <v>42.185313709286802</v>
+      </c>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
       <c r="K64" s="7"/>
     </row>
     <row r="65" ht="14.25">
@@ -6209,7 +6201,7 @@
         <v>5</v>
       </c>
       <c r="C66" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D66" s="4">
@@ -6217,15 +6209,24 @@
         <v>1</v>
       </c>
       <c r="E66" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F66"/>
+      <c r="F66">
+        <f>2*21.3713281308333</f>
+        <v>42.742656261666603</v>
+      </c>
       <c r="G66">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="7"/>
+        <v>153873.56254199977</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ref="H66:H75" si="13">G$66/G66</f>
+        <v>1</v>
+      </c>
+      <c r="K66" s="7">
+        <v>3013904</v>
+      </c>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="4">
@@ -6235,7 +6236,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D67" s="4">
@@ -6243,18 +6244,27 @@
         <v>2</v>
       </c>
       <c r="E67" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F67"/>
+      <c r="F67">
+        <f>2*13.3894052872222</f>
+        <v>26.7788105744444</v>
+      </c>
       <c r="G67">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="14" t="s">
+        <v>96403.718067999842</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="13"/>
+        <v>1.5961372198680417</v>
+      </c>
+      <c r="I67" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K67" s="7"/>
+      <c r="K67" s="7">
+        <v>3013903</v>
+      </c>
     </row>
     <row r="68" ht="14.25">
       <c r="A68" s="4">
@@ -6264,7 +6274,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D68" s="4">
@@ -6272,13 +6282,19 @@
         <v>4</v>
       </c>
       <c r="E68" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F68"/>
+      <c r="F68">
+        <v>10.282945034444399</v>
+      </c>
       <c r="G68">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>37018.602123999837</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="13"/>
+        <v>4.1566551331834525</v>
       </c>
       <c r="K68" s="7">
         <v>2968238</v>
@@ -6292,7 +6308,7 @@
         <v>5</v>
       </c>
       <c r="C69" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D69" s="4">
@@ -6300,7 +6316,7 @@
         <v>8</v>
       </c>
       <c r="E69" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F69">
@@ -6310,6 +6326,10 @@
         <f t="shared" si="10"/>
         <v>18036.962133999983</v>
       </c>
+      <c r="H69">
+        <f t="shared" si="13"/>
+        <v>8.5310132271079873</v>
+      </c>
       <c r="I69" s="6" t="s">
         <v>25</v>
       </c>
@@ -6328,7 +6348,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D70" s="4">
@@ -6336,7 +6356,7 @@
         <v>16</v>
       </c>
       <c r="E70" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F70">
@@ -6346,6 +6366,10 @@
         <f t="shared" si="10"/>
         <v>11661.310752000012</v>
       </c>
+      <c r="H70">
+        <f t="shared" si="13"/>
+        <v>13.19522014415139</v>
+      </c>
       <c r="I70" s="6" t="s">
         <v>26</v>
       </c>
@@ -6364,7 +6388,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D71" s="4">
@@ -6372,7 +6396,7 @@
         <v>32</v>
       </c>
       <c r="E71" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F71">
@@ -6382,6 +6406,10 @@
         <f t="shared" si="10"/>
         <v>5017.8288129999837</v>
       </c>
+      <c r="H71">
+        <f t="shared" si="13"/>
+        <v>30.665367089317694</v>
+      </c>
       <c r="I71" s="6" t="s">
         <v>27</v>
       </c>
@@ -6400,7 +6428,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D72" s="4">
@@ -6408,7 +6436,7 @@
         <v>64</v>
       </c>
       <c r="E72" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F72">
@@ -6418,6 +6446,10 @@
         <f t="shared" si="10"/>
         <v>3191.9559189999982</v>
       </c>
+      <c r="H72">
+        <f t="shared" si="13"/>
+        <v>48.206669028877606</v>
+      </c>
       <c r="I72" s="6" t="s">
         <v>28</v>
       </c>
@@ -6436,7 +6468,7 @@
         <v>5</v>
       </c>
       <c r="C73" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D73" s="4">
@@ -6444,7 +6476,7 @@
         <v>128</v>
       </c>
       <c r="E73" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F73">
@@ -6454,6 +6486,10 @@
         <f t="shared" si="10"/>
         <v>2303.6215190000007</v>
       </c>
+      <c r="H73">
+        <f t="shared" si="13"/>
+        <v>66.796373133723847</v>
+      </c>
       <c r="I73" s="6" t="s">
         <v>29</v>
       </c>
@@ -6472,25 +6508,30 @@
         <v>5</v>
       </c>
       <c r="C74" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D74">
         <v>256</v>
       </c>
       <c r="E74" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
       <c r="F74">
-        <v>0.74468592027777802</v>
+        <f>2*0.29755164</f>
+        <v>0.59510328000000001</v>
       </c>
       <c r="G74">
-        <f>3600*F74</f>
-        <v>2680.8693130000011</v>
+        <f t="shared" si="10"/>
+        <v>2142.3718079999999</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="13"/>
+        <v>71.823929892751735</v>
       </c>
       <c r="K74">
-        <v>2981373</v>
+        <v>3070290</v>
       </c>
     </row>
     <row r="75" ht="14.25">
@@ -6501,26 +6542,38 @@
         <v>5</v>
       </c>
       <c r="C75" s="4">
-        <f>2^-5</f>
+        <f t="shared" si="8"/>
         <v>0.03125</v>
       </c>
       <c r="D75">
         <v>512</v>
       </c>
       <c r="E75" s="4">
-        <f>32/256</f>
+        <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="F75">
-        <v>0.57972249638888895</v>
+      <c r="F75" s="4">
+        <f>2*0.289467022777778</f>
+        <v>0.57893404555555605</v>
       </c>
       <c r="G75">
-        <f>3600*F75</f>
-        <v>2087.0009870000004</v>
+        <f t="shared" si="10"/>
+        <v>2084.162564000002</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="13"/>
+        <v>73.829923442574426</v>
       </c>
       <c r="K75">
-        <v>2982462</v>
-      </c>
+        <v>3077713</v>
+      </c>
+    </row>
+    <row r="77" ht="14.25">
+      <c r="F77"/>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" ht="14.25">
+      <c r="F78"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/testResults/compilerResults/CompilerResults.xlsx
+++ b/testResults/compilerResults/CompilerResults.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Resolution</t>
   </si>
@@ -52,60 +52,6 @@
   </si>
   <si>
     <t xml:space="preserve">Time Hour</t>
-  </si>
-  <si>
-    <t>Node</t>
-  </si>
-  <si>
-    <t>cores</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c494: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c299: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c465: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c431: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c420: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c308: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c344: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c343: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c663: 192</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">c692: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c651: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c540: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c360: 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c435: 192</t>
   </si>
 </sst>
 </file>
@@ -481,7 +427,7 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr bwMode="auto">
-    <a:xfrm>
+    <a:xfrm rot="0">
       <a:off x="6562723" y="757235"/>
       <a:ext cx="4552949" cy="2724149"/>
     </a:xfrm>
@@ -813,7 +759,7 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr bwMode="auto">
-    <a:xfrm>
+    <a:xfrm rot="0">
       <a:off x="6562722" y="3576635"/>
       <a:ext cx="4552948" cy="2905124"/>
     </a:xfrm>
@@ -1145,7 +1091,7 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr bwMode="auto">
-    <a:xfrm>
+    <a:xfrm rot="0">
       <a:off x="7962898" y="7215186"/>
       <a:ext cx="4552949" cy="2905124"/>
     </a:xfrm>
@@ -1477,7 +1423,7 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr bwMode="auto">
-    <a:xfrm>
+    <a:xfrm rot="0">
       <a:off x="8229598" y="10301286"/>
       <a:ext cx="4552949" cy="3105149"/>
     </a:xfrm>
@@ -3883,7 +3829,7 @@
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="6562723" y="757235"/>
         <a:ext cx="4552949" cy="2724149"/>
       </xdr:xfrm>
@@ -3915,7 +3861,7 @@
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="6562722" y="3576635"/>
         <a:ext cx="4552948" cy="2905124"/>
       </xdr:xfrm>
@@ -3947,7 +3893,7 @@
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="7962898" y="7215186"/>
         <a:ext cx="4552949" cy="2905124"/>
       </xdr:xfrm>
@@ -3979,7 +3925,7 @@
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="8229598" y="10301286"/>
         <a:ext cx="4552949" cy="3105149"/>
       </xdr:xfrm>
@@ -5422,15 +5368,7 @@
       <c r="H43" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I43" t="s">
-        <v>12</v>
-      </c>
-      <c r="J43" t="s">
-        <v>13</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="K43" s="5"/>
     </row>
     <row r="44" ht="15">
       <c r="A44">
@@ -5462,15 +5400,9 @@
         <f t="shared" ref="H44:H53" si="11">G$44/G44</f>
         <v>1</v>
       </c>
-      <c r="I44" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J44" s="6">
-        <v>1</v>
-      </c>
-      <c r="K44" s="7">
-        <v>2942308</v>
-      </c>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="7"/>
     </row>
     <row r="45" ht="15">
       <c r="A45">
@@ -5502,15 +5434,9 @@
         <f t="shared" si="11"/>
         <v>1.6243970341572598</v>
       </c>
-      <c r="I45" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="K45" s="8">
-        <v>2942265</v>
-      </c>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="8"/>
     </row>
     <row r="46" ht="15">
       <c r="A46">
@@ -5542,15 +5468,9 @@
         <f t="shared" si="11"/>
         <v>3.1551949706549878</v>
       </c>
-      <c r="I46" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="K46" s="8">
-        <v>2942232</v>
-      </c>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="8"/>
     </row>
     <row r="47" ht="15">
       <c r="A47">
@@ -5582,15 +5502,9 @@
         <f t="shared" si="11"/>
         <v>5.5165222881345706</v>
       </c>
-      <c r="I47" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="6">
-        <v>7.9699999999999998</v>
-      </c>
-      <c r="K47" s="8">
-        <v>2940200</v>
-      </c>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="8"/>
     </row>
     <row r="48" ht="15">
       <c r="A48">
@@ -5624,9 +5538,7 @@
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="8">
-        <v>2935674</v>
-      </c>
+      <c r="K48" s="8"/>
     </row>
     <row r="49" ht="15">
       <c r="A49">
@@ -5658,9 +5570,7 @@
         <f t="shared" si="11"/>
         <v>17.79649519774361</v>
       </c>
-      <c r="K49" s="8">
-        <v>2935666</v>
-      </c>
+      <c r="K49" s="8"/>
     </row>
     <row r="50" ht="14.25">
       <c r="A50">
@@ -5692,9 +5602,7 @@
         <f t="shared" si="11"/>
         <v>34.229552151733465</v>
       </c>
-      <c r="K50" s="7">
-        <v>2935412</v>
-      </c>
+      <c r="K50" s="7"/>
     </row>
     <row r="51" ht="14.25">
       <c r="A51">
@@ -5726,9 +5634,7 @@
         <f t="shared" si="11"/>
         <v>42.74645191554113</v>
       </c>
-      <c r="K51" s="7">
-        <v>2935310</v>
-      </c>
+      <c r="K51" s="7"/>
     </row>
     <row r="52" ht="14.25">
       <c r="A52" s="2">
@@ -5749,15 +5655,15 @@
         <v>0.125</v>
       </c>
       <c r="F52" s="9">
-        <v>0.0083248658333333336</v>
+        <v>0.0077295838888888887</v>
       </c>
       <c r="G52">
         <f t="shared" si="10"/>
-        <v>29.969517</v>
+        <v>27.826501999999998</v>
       </c>
       <c r="H52">
         <f t="shared" si="11"/>
-        <v>41.000010844352225</v>
+        <v>44.157563246720649</v>
       </c>
       <c r="K52" s="7"/>
     </row>
@@ -5780,15 +5686,15 @@
         <v>0.125</v>
       </c>
       <c r="F53" s="9">
-        <v>0.034152586111111112</v>
+        <v>0.02887957722222222</v>
       </c>
       <c r="G53">
         <f t="shared" si="10"/>
-        <v>122.94931</v>
+        <v>103.966478</v>
       </c>
       <c r="H53">
         <f t="shared" si="11"/>
-        <v>9.9939602914404198</v>
+        <v>11.818718356507167</v>
       </c>
       <c r="K53" s="7"/>
     </row>
@@ -5828,15 +5734,9 @@
         <f t="shared" ref="H55:H64" si="12">G$55/G55</f>
         <v>1</v>
       </c>
-      <c r="I55" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="6">
-        <v>1</v>
-      </c>
-      <c r="K55" s="7">
-        <v>2944950</v>
-      </c>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="7"/>
     </row>
     <row r="56" ht="15">
       <c r="A56" s="4">
@@ -5868,15 +5768,9 @@
         <f t="shared" si="12"/>
         <v>1.0640964718134585</v>
       </c>
-      <c r="I56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="K56" s="7">
-        <v>2944937</v>
-      </c>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="7"/>
     </row>
     <row r="57" ht="15">
       <c r="A57" s="4">
@@ -5908,15 +5802,9 @@
         <f t="shared" si="12"/>
         <v>2.8098780962959817</v>
       </c>
-      <c r="I57" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J57" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="K57" s="7">
-        <v>2919149</v>
-      </c>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="7"/>
     </row>
     <row r="58" ht="15">
       <c r="A58" s="4">
@@ -5948,15 +5836,9 @@
         <f t="shared" si="12"/>
         <v>5.8297720789760756</v>
       </c>
-      <c r="I58" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" s="6">
-        <v>7.9699999999999998</v>
-      </c>
-      <c r="K58" s="7">
-        <v>2927478</v>
-      </c>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="7"/>
     </row>
     <row r="59" ht="15">
       <c r="A59" s="4">
@@ -5988,15 +5870,9 @@
         <f t="shared" si="12"/>
         <v>10.498007974984796</v>
       </c>
-      <c r="I59" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J59" s="6">
-        <v>15.94</v>
-      </c>
-      <c r="K59" s="7">
-        <v>2917264</v>
-      </c>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="7"/>
     </row>
     <row r="60" ht="15">
       <c r="A60" s="4">
@@ -6028,15 +5904,9 @@
         <f t="shared" si="12"/>
         <v>19.841722161182016</v>
       </c>
-      <c r="I60" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" s="6">
-        <v>31.870000000000001</v>
-      </c>
-      <c r="K60" s="7">
-        <v>2917262</v>
-      </c>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="7"/>
     </row>
     <row r="61" ht="15">
       <c r="A61" s="4">
@@ -6068,15 +5938,9 @@
         <f t="shared" si="12"/>
         <v>32.320262475220026</v>
       </c>
-      <c r="I61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J61" s="6">
-        <v>63.710000000000001</v>
-      </c>
-      <c r="K61" s="7">
-        <v>2915598</v>
-      </c>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="7"/>
     </row>
     <row r="62" ht="15">
       <c r="A62" s="4">
@@ -6108,15 +5972,9 @@
         <f t="shared" si="12"/>
         <v>44.344136191180056</v>
       </c>
-      <c r="I62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J62" s="6">
-        <v>127.36</v>
-      </c>
-      <c r="K62" s="7">
-        <v>2915566</v>
-      </c>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="7"/>
     </row>
     <row r="63" ht="15">
       <c r="A63" s="4">
@@ -6137,22 +5995,19 @@
         <v>0.125</v>
       </c>
       <c r="F63" s="9">
-        <f>2*0.0333151991666667</f>
-        <v>0.066630398333333396</v>
+        <v>0.063546028611111111</v>
       </c>
       <c r="G63">
         <f t="shared" si="10"/>
-        <v>239.86943400000024</v>
+        <v>228.765703</v>
       </c>
       <c r="H63">
         <f t="shared" si="12"/>
-        <v>45.820495857758921</v>
+        <v>48.044511318202225</v>
       </c>
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="7">
-        <v>3087445</v>
-      </c>
+      <c r="K63" s="7"/>
     </row>
     <row r="64" ht="15">
       <c r="A64" s="4">
@@ -6173,16 +6028,15 @@
         <v>0.125</v>
       </c>
       <c r="F64" s="9">
-        <f>2*0.03618602805555556</f>
-        <v>0.072372056111111124</v>
+        <v>0.069991277500000004</v>
       </c>
       <c r="G64">
         <f t="shared" si="10"/>
-        <v>260.53940200000005</v>
+        <v>251.96859900000001</v>
       </c>
       <c r="H64">
         <f t="shared" si="12"/>
-        <v>42.185313709286802</v>
+        <v>43.620262408174078</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
@@ -6224,9 +6078,7 @@
         <f t="shared" ref="H66:H75" si="13">G$66/G66</f>
         <v>1</v>
       </c>
-      <c r="K66" s="7">
-        <v>3013904</v>
-      </c>
+      <c r="K66" s="7"/>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="4">
@@ -6259,12 +6111,8 @@
         <f t="shared" si="13"/>
         <v>1.5961372198680417</v>
       </c>
-      <c r="I67" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K67" s="7">
-        <v>3013903</v>
-      </c>
+      <c r="I67" s="10"/>
+      <c r="K67" s="7"/>
     </row>
     <row r="68" ht="14.25">
       <c r="A68" s="4">
@@ -6296,9 +6144,7 @@
         <f t="shared" si="13"/>
         <v>4.1566551331834525</v>
       </c>
-      <c r="K68" s="7">
-        <v>2968238</v>
-      </c>
+      <c r="K68" s="7"/>
     </row>
     <row r="69" ht="14.25">
       <c r="A69" s="4">
@@ -6330,15 +6176,9 @@
         <f t="shared" si="13"/>
         <v>8.5310132271079873</v>
       </c>
-      <c r="I69" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J69" s="6">
-        <v>7.9699999999999998</v>
-      </c>
-      <c r="K69" s="7">
-        <v>2887572</v>
-      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="7"/>
     </row>
     <row r="70" ht="14.25">
       <c r="A70" s="4">
@@ -6370,15 +6210,9 @@
         <f t="shared" si="13"/>
         <v>13.19522014415139</v>
       </c>
-      <c r="I70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J70" s="6">
-        <v>15.94</v>
-      </c>
-      <c r="K70" s="7">
-        <v>2887528</v>
-      </c>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="7"/>
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="4">
@@ -6410,15 +6244,9 @@
         <f t="shared" si="13"/>
         <v>30.665367089317694</v>
       </c>
-      <c r="I71" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J71" s="6">
-        <v>31.870000000000001</v>
-      </c>
-      <c r="K71" s="7">
-        <v>2863616</v>
-      </c>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="7"/>
     </row>
     <row r="72" ht="14.25">
       <c r="A72" s="4">
@@ -6450,15 +6278,9 @@
         <f t="shared" si="13"/>
         <v>48.206669028877606</v>
       </c>
-      <c r="I72" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J72" s="6">
-        <v>63.710000000000001</v>
-      </c>
-      <c r="K72" s="7">
-        <v>2862265</v>
-      </c>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="7"/>
     </row>
     <row r="73" ht="14.25">
       <c r="A73" s="4">
@@ -6490,15 +6312,9 @@
         <f t="shared" si="13"/>
         <v>66.796373133723847</v>
       </c>
-      <c r="I73" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J73" s="6">
-        <v>127.31</v>
-      </c>
-      <c r="K73" s="7">
-        <v>2859759</v>
-      </c>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="7"/>
     </row>
     <row r="74" ht="14.25">
       <c r="A74">
@@ -6519,20 +6335,17 @@
         <v>0.125</v>
       </c>
       <c r="F74">
-        <f>2*0.29755164</f>
-        <v>0.59510328000000001</v>
+        <v>0.54213655138888905</v>
       </c>
       <c r="G74">
         <f t="shared" si="10"/>
-        <v>2142.3718079999999</v>
+        <v>1951.6915850000005</v>
       </c>
       <c r="H74">
         <f t="shared" si="13"/>
-        <v>71.823929892751735</v>
-      </c>
-      <c r="K74">
-        <v>3070290</v>
-      </c>
+        <v>78.841126192589357</v>
+      </c>
+      <c r="K74"/>
     </row>
     <row r="75" ht="14.25">
       <c r="A75">
@@ -6553,20 +6366,17 @@
         <v>0.125</v>
       </c>
       <c r="F75" s="4">
-        <f>2*0.289467022777778</f>
-        <v>0.57893404555555605</v>
+        <v>0.42326655083333298</v>
       </c>
       <c r="G75">
         <f t="shared" si="10"/>
-        <v>2084.162564000002</v>
+        <v>1523.7595829999987</v>
       </c>
       <c r="H75">
         <f t="shared" si="13"/>
-        <v>73.829923442574426</v>
-      </c>
-      <c r="K75">
-        <v>3077713</v>
-      </c>
+        <v>100.98283499490871</v>
+      </c>
+      <c r="K75"/>
     </row>
     <row r="77" ht="14.25">
       <c r="F77"/>

--- a/testResults/compilerResults/CompilerResults.xlsx
+++ b/testResults/compilerResults/CompilerResults.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Resolution</t>
   </si>
@@ -51,7 +51,13 @@
     <t xml:space="preserve">full node</t>
   </si>
   <si>
+    <t>nibi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Time Hour</t>
+  </si>
+  <si>
+    <t>trillium</t>
   </si>
 </sst>
 </file>
@@ -102,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
@@ -122,6 +128,9 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5342,6 +5351,9 @@
       <c r="E42" t="s">
         <v>10</v>
       </c>
+      <c r="F42" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="4" t="s">
@@ -5360,7 +5372,7 @@
         <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>6</v>
@@ -5378,7 +5390,7 @@
         <v>5</v>
       </c>
       <c r="C44">
-        <f t="shared" ref="C44:C75" si="8">2^-5</f>
+        <f t="shared" ref="C44:C107" si="8">2^-5</f>
         <v>0.03125</v>
       </c>
       <c r="D44">
@@ -5386,14 +5398,14 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <f t="shared" ref="E44:E75" si="9">32/256</f>
+        <f t="shared" ref="E44:E107" si="9">32/256</f>
         <v>0.125</v>
       </c>
       <c r="F44">
         <v>0.34131958944444402</v>
       </c>
       <c r="G44">
-        <f t="shared" ref="G44:G75" si="10">3600*F44</f>
+        <f t="shared" ref="G44:G99" si="10">3600*F44</f>
         <v>1228.7505219999985</v>
       </c>
       <c r="H44">
@@ -6146,7 +6158,7 @@
       </c>
       <c r="K68" s="7"/>
     </row>
-    <row r="69" ht="14.25">
+    <row r="69" ht="15">
       <c r="A69" s="4">
         <v>1024</v>
       </c>
@@ -6180,7 +6192,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" ht="14.25">
+    <row r="70" ht="15">
       <c r="A70" s="4">
         <v>1024</v>
       </c>
@@ -6214,7 +6226,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="7"/>
     </row>
-    <row r="71" ht="14.25">
+    <row r="71" ht="15">
       <c r="A71" s="4">
         <v>1024</v>
       </c>
@@ -6248,7 +6260,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" ht="14.25">
+    <row r="72" ht="15">
       <c r="A72" s="4">
         <v>1024</v>
       </c>
@@ -6282,7 +6294,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="7"/>
     </row>
-    <row r="73" ht="14.25">
+    <row r="73" ht="15">
       <c r="A73" s="4">
         <v>1024</v>
       </c>
@@ -6378,12 +6390,1027 @@
       </c>
       <c r="K75"/>
     </row>
+    <row r="76" ht="14.25">
+      <c r="G76"/>
+    </row>
     <row r="77" ht="14.25">
-      <c r="F77"/>
-      <c r="G77" s="4"/>
+      <c r="A77">
+        <v>2048</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+      <c r="C77" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D77">
+        <v>512</v>
+      </c>
+      <c r="E77" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F77">
+        <f>5*0.974503001944444</f>
+        <v>4.8725150097222194</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="10"/>
+        <v>17541.05403499999</v>
+      </c>
     </row>
     <row r="78" ht="14.25">
       <c r="F78"/>
+    </row>
+    <row r="84" ht="14.25">
+      <c r="A84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" ht="14.25">
+      <c r="A85" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" ht="14.25">
+      <c r="A86" s="4">
+        <v>256</v>
+      </c>
+      <c r="B86" s="4">
+        <v>5</v>
+      </c>
+      <c r="C86" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D86" s="4">
+        <f>2^0</f>
+        <v>1</v>
+      </c>
+      <c r="E86" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0.20240351916666699</v>
+      </c>
+      <c r="G86" s="4">
+        <f t="shared" si="10"/>
+        <v>728.6526690000012</v>
+      </c>
+      <c r="H86" s="4">
+        <f t="shared" ref="H86:H95" si="14">G$86/G86</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" ht="14.25">
+      <c r="A87" s="4">
+        <v>256</v>
+      </c>
+      <c r="B87" s="4">
+        <v>5</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D87">
+        <f>2^1</f>
+        <v>2</v>
+      </c>
+      <c r="E87" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F87" s="4">
+        <v>0.15878702583333301</v>
+      </c>
+      <c r="G87" s="4">
+        <f t="shared" si="10"/>
+        <v>571.63329299999884</v>
+      </c>
+      <c r="H87" s="4">
+        <f t="shared" si="14"/>
+        <v>1.2746854984179563</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25">
+      <c r="A88" s="4">
+        <v>256</v>
+      </c>
+      <c r="B88" s="4">
+        <v>5</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D88">
+        <f>2^2</f>
+        <v>4</v>
+      </c>
+      <c r="E88" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F88" s="11">
+        <v>0.059740939166666673</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="10"/>
+        <v>215.06738100000001</v>
+      </c>
+      <c r="H88" s="4">
+        <f t="shared" si="14"/>
+        <v>3.3880203758095755</v>
+      </c>
+    </row>
+    <row r="89" ht="14.25">
+      <c r="A89" s="4">
+        <v>256</v>
+      </c>
+      <c r="B89" s="4">
+        <v>5</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D89">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="E89" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F89" s="9">
+        <v>0.029952288055555561</v>
+      </c>
+      <c r="G89" s="4">
+        <f t="shared" si="10"/>
+        <v>107.82823700000002</v>
+      </c>
+      <c r="H89" s="4">
+        <f t="shared" si="14"/>
+        <v>6.7575311372289351</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25">
+      <c r="A90" s="4">
+        <v>256</v>
+      </c>
+      <c r="B90" s="4">
+        <v>5</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D90">
+        <f>2^4</f>
+        <v>16</v>
+      </c>
+      <c r="E90" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F90" s="9">
+        <v>0.015226363611111109</v>
+      </c>
+      <c r="G90" s="4">
+        <f t="shared" si="10"/>
+        <v>54.814908999999993</v>
+      </c>
+      <c r="H90" s="4">
+        <f t="shared" si="14"/>
+        <v>13.292965039858066</v>
+      </c>
+    </row>
+    <row r="91" ht="14.25">
+      <c r="A91" s="4">
+        <v>256</v>
+      </c>
+      <c r="B91" s="4">
+        <v>5</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D91">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E91" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F91" s="9">
+        <v>0.010068166944444439</v>
+      </c>
+      <c r="G91" s="4">
+        <f t="shared" si="10"/>
+        <v>36.24540099999998</v>
+      </c>
+      <c r="H91" s="4">
+        <f t="shared" si="14"/>
+        <v>20.103313769380055</v>
+      </c>
+    </row>
+    <row r="92" ht="14.25">
+      <c r="A92" s="4">
+        <v>256</v>
+      </c>
+      <c r="B92" s="4">
+        <v>5</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D92">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E92" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F92" s="9">
+        <v>0.011229834722222221</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="10"/>
+        <v>40.427404999999993</v>
+      </c>
+      <c r="H92" s="4">
+        <f t="shared" si="14"/>
+        <v>18.023730907289284</v>
+      </c>
+    </row>
+    <row r="93" ht="14.25">
+      <c r="A93" s="4">
+        <v>256</v>
+      </c>
+      <c r="B93" s="4">
+        <v>5</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D93">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E93" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F93" s="9">
+        <v>0.0070462197222222224</v>
+      </c>
+      <c r="G93" s="4">
+        <f t="shared" si="10"/>
+        <v>25.366391</v>
+      </c>
+      <c r="H93" s="4">
+        <f t="shared" si="14"/>
+        <v>28.725121717157212</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25">
+      <c r="A94">
+        <v>256</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
+      </c>
+      <c r="C94" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D94">
+        <v>256</v>
+      </c>
+      <c r="E94" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F94" s="9">
+        <v>0.0053327986111111111</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="10"/>
+        <v>19.198074999999999</v>
+      </c>
+      <c r="H94" s="4">
+        <f t="shared" si="14"/>
+        <v>37.954465174242792</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25">
+      <c r="A95">
+        <v>256</v>
+      </c>
+      <c r="B95">
+        <v>5</v>
+      </c>
+      <c r="C95" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D95">
+        <v>512</v>
+      </c>
+      <c r="E95" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F95" s="9">
+        <v>0.0098542594444444454</v>
+      </c>
+      <c r="G95" s="4">
+        <f t="shared" si="10"/>
+        <v>35.475334000000004</v>
+      </c>
+      <c r="H95" s="4">
+        <f t="shared" si="14"/>
+        <v>20.539698625529532</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" ht="14.25">
+      <c r="A97" s="4">
+        <v>512</v>
+      </c>
+      <c r="B97" s="4">
+        <v>5</v>
+      </c>
+      <c r="C97" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D97" s="4">
+        <f>2^0</f>
+        <v>1</v>
+      </c>
+      <c r="E97" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1.69314931638889</v>
+      </c>
+      <c r="G97" s="4">
+        <f t="shared" si="10"/>
+        <v>6095.3375390000037</v>
+      </c>
+      <c r="H97" s="4">
+        <f t="shared" ref="H97:H99" si="15">G$97/G97</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25">
+      <c r="A98" s="4">
+        <v>512</v>
+      </c>
+      <c r="B98" s="4">
+        <v>5</v>
+      </c>
+      <c r="C98" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D98" s="4">
+        <f>2^1</f>
+        <v>2</v>
+      </c>
+      <c r="E98" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F98" s="4">
+        <v>1.2984636161111101</v>
+      </c>
+      <c r="G98" s="4">
+        <f t="shared" si="10"/>
+        <v>4674.4690179999961</v>
+      </c>
+      <c r="H98" s="4">
+        <f t="shared" si="15"/>
+        <v>1.3039636192963657</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25">
+      <c r="A99" s="4">
+        <v>512</v>
+      </c>
+      <c r="B99" s="4">
+        <v>5</v>
+      </c>
+      <c r="C99" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D99" s="4">
+        <f>2^2</f>
+        <v>4</v>
+      </c>
+      <c r="E99" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F99" s="4">
+        <v>0.51835641222222195</v>
+      </c>
+      <c r="G99" s="4">
+        <f t="shared" si="10"/>
+        <v>1866.083083999999</v>
+      </c>
+      <c r="H99" s="4">
+        <f t="shared" si="15"/>
+        <v>3.2663805761180176</v>
+      </c>
+    </row>
+    <row r="100" ht="14.25">
+      <c r="A100" s="4">
+        <v>512</v>
+      </c>
+      <c r="B100" s="4">
+        <v>5</v>
+      </c>
+      <c r="C100" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D100" s="4">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="E100" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F100" s="4">
+        <v>0.25844555611111097</v>
+      </c>
+      <c r="G100" s="4">
+        <f t="shared" ref="G100:G117" si="16">3600*F100</f>
+        <v>930.40400199999954</v>
+      </c>
+      <c r="H100" s="4">
+        <f t="shared" ref="H100:H106" si="17">G$97/G100</f>
+        <v>6.5512804393547812</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25">
+      <c r="A101" s="4">
+        <v>512</v>
+      </c>
+      <c r="B101" s="4">
+        <v>5</v>
+      </c>
+      <c r="C101" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D101" s="4">
+        <f>2^4</f>
+        <v>16</v>
+      </c>
+      <c r="E101" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0.145954053333333</v>
+      </c>
+      <c r="G101" s="4">
+        <f t="shared" si="16"/>
+        <v>525.43459199999882</v>
+      </c>
+      <c r="H101" s="4">
+        <f t="shared" si="17"/>
+        <v>11.600563860477648</v>
+      </c>
+    </row>
+    <row r="102" ht="14.25">
+      <c r="A102" s="4">
+        <v>512</v>
+      </c>
+      <c r="B102" s="4">
+        <v>5</v>
+      </c>
+      <c r="C102" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D102" s="4">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E102" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F102" s="4">
+        <v>0.102612797222222</v>
+      </c>
+      <c r="G102" s="4">
+        <f t="shared" si="16"/>
+        <v>369.4060699999992</v>
+      </c>
+      <c r="H102" s="4">
+        <f t="shared" si="17"/>
+        <v>16.500371905096245</v>
+      </c>
+    </row>
+    <row r="103" ht="14.25">
+      <c r="A103" s="4">
+        <v>512</v>
+      </c>
+      <c r="B103" s="4">
+        <v>5</v>
+      </c>
+      <c r="C103" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D103" s="4">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E103" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F103" s="9">
+        <v>0.083577313888888893</v>
+      </c>
+      <c r="G103" s="4">
+        <f t="shared" si="16"/>
+        <v>300.87833000000001</v>
+      </c>
+      <c r="H103" s="4">
+        <f t="shared" si="17"/>
+        <v>20.258479695098028</v>
+      </c>
+    </row>
+    <row r="104" ht="14.25">
+      <c r="A104" s="4">
+        <v>512</v>
+      </c>
+      <c r="B104" s="4">
+        <v>5</v>
+      </c>
+      <c r="C104" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D104" s="4">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E104" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F104" s="9">
+        <v>0.08124256888888888</v>
+      </c>
+      <c r="G104" s="4">
+        <f t="shared" si="16"/>
+        <v>292.47324799999996</v>
+      </c>
+      <c r="H104" s="4">
+        <f t="shared" si="17"/>
+        <v>20.840666900926283</v>
+      </c>
+    </row>
+    <row r="105" ht="14.25">
+      <c r="A105" s="4">
+        <v>512</v>
+      </c>
+      <c r="B105" s="4">
+        <v>5</v>
+      </c>
+      <c r="C105" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D105">
+        <v>256</v>
+      </c>
+      <c r="E105" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F105" s="9">
+        <v>0.04398438027777777</v>
+      </c>
+      <c r="G105" s="4">
+        <f t="shared" si="16"/>
+        <v>158.34376899999998</v>
+      </c>
+      <c r="H105" s="4">
+        <f t="shared" si="17"/>
+        <v>38.49433152623773</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25">
+      <c r="A106" s="4">
+        <v>512</v>
+      </c>
+      <c r="B106" s="4">
+        <v>5</v>
+      </c>
+      <c r="C106" s="4">
+        <f t="shared" si="8"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D106">
+        <v>512</v>
+      </c>
+      <c r="E106" s="4">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+      <c r="F106" s="9">
+        <v>0.048619712500000002</v>
+      </c>
+      <c r="G106" s="4">
+        <f t="shared" si="16"/>
+        <v>175.03096500000001</v>
+      </c>
+      <c r="H106" s="4">
+        <f t="shared" si="17"/>
+        <v>34.824338304939374</v>
+      </c>
+    </row>
+    <row r="107" ht="14.25">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" ht="14.25">
+      <c r="A108" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B108" s="4">
+        <v>5</v>
+      </c>
+      <c r="C108" s="4">
+        <f t="shared" ref="C108:C117" si="18">2^-5</f>
+        <v>0.03125</v>
+      </c>
+      <c r="D108" s="4">
+        <f>2^0</f>
+        <v>1</v>
+      </c>
+      <c r="E108" s="4">
+        <f t="shared" ref="E108:E117" si="19">32/256</f>
+        <v>0.125</v>
+      </c>
+      <c r="F108" s="4">
+        <f>2*9.33391268083333</f>
+        <v>18.667825361666662</v>
+      </c>
+      <c r="G108" s="4">
+        <f t="shared" si="16"/>
+        <v>67204.171301999988</v>
+      </c>
+      <c r="H108" s="4">
+        <f t="shared" ref="H108:H117" si="20">G$108/G108</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" ht="14.25">
+      <c r="A109" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B109" s="4">
+        <v>5</v>
+      </c>
+      <c r="C109" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D109" s="4">
+        <f>2^1</f>
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F109" s="4">
+        <f>2*6.91067686722222</f>
+        <v>13.82135373444444</v>
+      </c>
+      <c r="G109" s="4">
+        <f t="shared" si="16"/>
+        <v>49756.873443999983</v>
+      </c>
+      <c r="H109" s="4">
+        <f t="shared" si="20"/>
+        <v>1.3506510086015848</v>
+      </c>
+    </row>
+    <row r="110" ht="14.25">
+      <c r="A110" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B110" s="4">
+        <v>5</v>
+      </c>
+      <c r="C110" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D110" s="4">
+        <f>2^2</f>
+        <v>4</v>
+      </c>
+      <c r="E110" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F110" s="4">
+        <f>2*2.59001884555556</f>
+        <v>5.1800376911111199</v>
+      </c>
+      <c r="G110" s="4">
+        <f t="shared" si="16"/>
+        <v>18648.135688000031</v>
+      </c>
+      <c r="H110" s="4">
+        <f t="shared" si="20"/>
+        <v>3.6038010676448202</v>
+      </c>
+    </row>
+    <row r="111" ht="14.25">
+      <c r="A111" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B111" s="4">
+        <v>5</v>
+      </c>
+      <c r="C111" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D111" s="4">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="E111" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F111" s="4">
+        <v>2.2341993200000001</v>
+      </c>
+      <c r="G111" s="4">
+        <f t="shared" si="16"/>
+        <v>8043.1175520000006</v>
+      </c>
+      <c r="H111" s="4">
+        <f t="shared" si="20"/>
+        <v>8.3554878898032534</v>
+      </c>
+    </row>
+    <row r="112" ht="14.25">
+      <c r="A112" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B112" s="4">
+        <v>5</v>
+      </c>
+      <c r="C112" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D112" s="4">
+        <f>2^4</f>
+        <v>16</v>
+      </c>
+      <c r="E112" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F112" s="4">
+        <v>1.2661140711111101</v>
+      </c>
+      <c r="G112" s="4">
+        <f t="shared" si="16"/>
+        <v>4558.0106559999958</v>
+      </c>
+      <c r="H112" s="4">
+        <f t="shared" si="20"/>
+        <v>14.744189159262916</v>
+      </c>
+    </row>
+    <row r="113" ht="14.25">
+      <c r="A113" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B113" s="4">
+        <v>5</v>
+      </c>
+      <c r="C113" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D113" s="4">
+        <f>2^5</f>
+        <v>32</v>
+      </c>
+      <c r="E113" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F113" s="4">
+        <v>0.92103260305555601</v>
+      </c>
+      <c r="G113" s="4">
+        <f t="shared" si="16"/>
+        <v>3315.7173710000015</v>
+      </c>
+      <c r="H113" s="4">
+        <f t="shared" si="20"/>
+        <v>20.268365419134501</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25">
+      <c r="A114" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B114" s="4">
+        <v>5</v>
+      </c>
+      <c r="C114" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D114" s="4">
+        <f>2^6</f>
+        <v>64</v>
+      </c>
+      <c r="E114" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F114" s="4">
+        <v>0.68911994444444402</v>
+      </c>
+      <c r="G114" s="4">
+        <f t="shared" si="16"/>
+        <v>2480.8317999999986</v>
+      </c>
+      <c r="H114" s="4">
+        <f t="shared" si="20"/>
+        <v>27.089370307974942</v>
+      </c>
+    </row>
+    <row r="115" ht="14.25">
+      <c r="A115" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B115" s="4">
+        <v>5</v>
+      </c>
+      <c r="C115" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D115" s="4">
+        <f>2^7</f>
+        <v>128</v>
+      </c>
+      <c r="E115" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0.67225378222222198</v>
+      </c>
+      <c r="G115" s="4">
+        <f t="shared" si="16"/>
+        <v>2420.1136159999992</v>
+      </c>
+      <c r="H115" s="4">
+        <f t="shared" si="20"/>
+        <v>27.769014999004909</v>
+      </c>
+    </row>
+    <row r="116" ht="14.25">
+      <c r="A116" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B116" s="4">
+        <v>5</v>
+      </c>
+      <c r="C116" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D116" s="4">
+        <v>256</v>
+      </c>
+      <c r="E116" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0.476966736666667</v>
+      </c>
+      <c r="G116" s="4">
+        <f t="shared" si="16"/>
+        <v>1717.0802520000011</v>
+      </c>
+      <c r="H116" s="4">
+        <f t="shared" si="20"/>
+        <v>39.138631536716282</v>
+      </c>
+    </row>
+    <row r="117" ht="14.25">
+      <c r="A117" s="4">
+        <v>1024</v>
+      </c>
+      <c r="B117" s="4">
+        <v>5</v>
+      </c>
+      <c r="C117" s="4">
+        <f t="shared" si="18"/>
+        <v>0.03125</v>
+      </c>
+      <c r="D117" s="4">
+        <v>512</v>
+      </c>
+      <c r="E117" s="4">
+        <f t="shared" si="19"/>
+        <v>0.125</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0.29459462555555599</v>
+      </c>
+      <c r="G117" s="4">
+        <f t="shared" si="16"/>
+        <v>1060.5406520000015</v>
+      </c>
+      <c r="H117" s="4">
+        <f t="shared" si="20"/>
+        <v>63.367840898191133</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
